--- a/Data/EXCEL/Transfer/salemon/202208/3432-salemon-202208.xlsx
+++ b/Data/EXCEL/Transfer/salemon/202208/3432-salemon-202208.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\WORKSPACES\GoodinfoWebData\salemon\202208\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\WORKSPACES\xls2xlsx\Transfer\202208\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5859275E-8E3B-4E3D-8467-8E16C0FF0503}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C05CB10B-774C-47F6-A3E4-3CACC668CB68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3270" yWindow="735" windowWidth="22035" windowHeight="12855"/>
+    <workbookView xWindow="390" yWindow="390" windowWidth="30645" windowHeight="19905"/>
   </bookViews>
   <sheets>
     <sheet name="3432-salemon-202208" sheetId="2" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="890" uniqueCount="18">
   <si>
     <t>月別</t>
   </si>
@@ -72,12 +72,15 @@
   <si>
     <t>年增</t>
   </si>
+  <si>
+    <t>-</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="25" x14ac:knownFonts="1">
+  <fonts count="26" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -243,7 +246,7 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="新細明體"/>
-      <family val="2"/>
+      <family val="1"/>
       <charset val="136"/>
       <scheme val="minor"/>
     </font>
@@ -260,7 +263,7 @@
       <sz val="10"/>
       <color rgb="FFFF0000"/>
       <name val="新細明體"/>
-      <family val="2"/>
+      <family val="1"/>
       <charset val="136"/>
       <scheme val="minor"/>
     </font>
@@ -268,13 +271,21 @@
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="新細明體"/>
-      <family val="2"/>
+      <family val="1"/>
       <charset val="136"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF008000"/>
+      <name val="新細明體"/>
+      <family val="1"/>
+      <charset val="136"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
       <name val="新細明體"/>
       <family val="2"/>
       <charset val="136"/>
@@ -815,7 +826,7 @@
     <xf numFmtId="0" fontId="18" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="33" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -824,7 +835,7 @@
     <xf numFmtId="0" fontId="20" fillId="33" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="17" fontId="19" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -842,22 +853,22 @@
     <xf numFmtId="0" fontId="23" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1215,20 +1226,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Q63"/>
+  <dimension ref="A1:Q211"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.625" customWidth="1"/>
-    <col min="2" max="6" width="9.75" customWidth="1"/>
-    <col min="7" max="7" width="10.625" customWidth="1"/>
-    <col min="8" max="8" width="11.125" customWidth="1"/>
-    <col min="9" max="10" width="9.75" customWidth="1"/>
-    <col min="11" max="11" width="11.125" customWidth="1"/>
-    <col min="12" max="12" width="9.25" customWidth="1"/>
-    <col min="13" max="13" width="11.125" customWidth="1"/>
-    <col min="14" max="15" width="9.75" customWidth="1"/>
-    <col min="16" max="16" width="11.125" customWidth="1"/>
-    <col min="17" max="17" width="10.5" customWidth="1"/>
+    <col min="1" max="1" width="15.75" customWidth="1"/>
+    <col min="2" max="6" width="13.25" customWidth="1"/>
+    <col min="7" max="7" width="14.5" customWidth="1"/>
+    <col min="8" max="8" width="15.125" customWidth="1"/>
+    <col min="9" max="10" width="13.25" customWidth="1"/>
+    <col min="11" max="13" width="15.125" customWidth="1"/>
+    <col min="14" max="15" width="13.25" customWidth="1"/>
+    <col min="16" max="16" width="15.125" customWidth="1"/>
+    <col min="17" max="17" width="13.125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
@@ -4504,6 +4513,7850 @@
       </c>
       <c r="Q63" s="10">
         <v>-48.8</v>
+      </c>
+    </row>
+    <row r="64" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A64" s="6">
+        <v>42979</v>
+      </c>
+      <c r="B64" s="7">
+        <v>12.75</v>
+      </c>
+      <c r="C64" s="7">
+        <v>12.95</v>
+      </c>
+      <c r="D64" s="7">
+        <v>14.6</v>
+      </c>
+      <c r="E64" s="7">
+        <v>12.45</v>
+      </c>
+      <c r="F64" s="8">
+        <v>0.35</v>
+      </c>
+      <c r="G64" s="8">
+        <v>2.78</v>
+      </c>
+      <c r="H64" s="9">
+        <v>0.156</v>
+      </c>
+      <c r="I64" s="8">
+        <v>7.53</v>
+      </c>
+      <c r="J64" s="10">
+        <v>-55.8</v>
+      </c>
+      <c r="K64" s="9">
+        <v>1.68</v>
+      </c>
+      <c r="L64" s="10">
+        <v>-50.3</v>
+      </c>
+      <c r="M64" s="9">
+        <v>0.156</v>
+      </c>
+      <c r="N64" s="8">
+        <v>7.53</v>
+      </c>
+      <c r="O64" s="10">
+        <v>-55.8</v>
+      </c>
+      <c r="P64" s="9">
+        <v>1.68</v>
+      </c>
+      <c r="Q64" s="10">
+        <v>-50.3</v>
+      </c>
+    </row>
+    <row r="65" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A65" s="6">
+        <v>42948</v>
+      </c>
+      <c r="B65" s="7">
+        <v>12.65</v>
+      </c>
+      <c r="C65" s="7">
+        <v>12.6</v>
+      </c>
+      <c r="D65" s="7">
+        <v>13.5</v>
+      </c>
+      <c r="E65" s="7">
+        <v>11.7</v>
+      </c>
+      <c r="F65" s="10">
+        <v>-0.05</v>
+      </c>
+      <c r="G65" s="10">
+        <v>-0.4</v>
+      </c>
+      <c r="H65" s="9">
+        <v>0.14499999999999999</v>
+      </c>
+      <c r="I65" s="8">
+        <v>2.06</v>
+      </c>
+      <c r="J65" s="10">
+        <v>-61.6</v>
+      </c>
+      <c r="K65" s="9">
+        <v>1.53</v>
+      </c>
+      <c r="L65" s="10">
+        <v>-49.6</v>
+      </c>
+      <c r="M65" s="9">
+        <v>0.14499999999999999</v>
+      </c>
+      <c r="N65" s="8">
+        <v>2.06</v>
+      </c>
+      <c r="O65" s="10">
+        <v>-61.6</v>
+      </c>
+      <c r="P65" s="9">
+        <v>1.53</v>
+      </c>
+      <c r="Q65" s="10">
+        <v>-49.6</v>
+      </c>
+    </row>
+    <row r="66" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A66" s="6">
+        <v>42917</v>
+      </c>
+      <c r="B66" s="7">
+        <v>14.55</v>
+      </c>
+      <c r="C66" s="7">
+        <v>12.65</v>
+      </c>
+      <c r="D66" s="7">
+        <v>15.35</v>
+      </c>
+      <c r="E66" s="7">
+        <v>12.4</v>
+      </c>
+      <c r="F66" s="10">
+        <v>-1.85</v>
+      </c>
+      <c r="G66" s="10">
+        <v>-12.76</v>
+      </c>
+      <c r="H66" s="9">
+        <v>0.14199999999999999</v>
+      </c>
+      <c r="I66" s="10">
+        <v>-23.4</v>
+      </c>
+      <c r="J66" s="10">
+        <v>-58.7</v>
+      </c>
+      <c r="K66" s="9">
+        <v>1.38</v>
+      </c>
+      <c r="L66" s="10">
+        <v>-47.9</v>
+      </c>
+      <c r="M66" s="9">
+        <v>0.14199999999999999</v>
+      </c>
+      <c r="N66" s="10">
+        <v>-23.4</v>
+      </c>
+      <c r="O66" s="10">
+        <v>-58.7</v>
+      </c>
+      <c r="P66" s="9">
+        <v>1.38</v>
+      </c>
+      <c r="Q66" s="10">
+        <v>-47.9</v>
+      </c>
+    </row>
+    <row r="67" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A67" s="6">
+        <v>42887</v>
+      </c>
+      <c r="B67" s="7">
+        <v>11.8</v>
+      </c>
+      <c r="C67" s="7">
+        <v>14.5</v>
+      </c>
+      <c r="D67" s="7">
+        <v>16.399999999999999</v>
+      </c>
+      <c r="E67" s="7">
+        <v>11.75</v>
+      </c>
+      <c r="F67" s="8">
+        <v>2.8</v>
+      </c>
+      <c r="G67" s="8">
+        <v>23.93</v>
+      </c>
+      <c r="H67" s="9">
+        <v>0.186</v>
+      </c>
+      <c r="I67" s="10">
+        <v>-16.2</v>
+      </c>
+      <c r="J67" s="10">
+        <v>-44.6</v>
+      </c>
+      <c r="K67" s="9">
+        <v>1.24</v>
+      </c>
+      <c r="L67" s="10">
+        <v>-46.3</v>
+      </c>
+      <c r="M67" s="9">
+        <v>0.186</v>
+      </c>
+      <c r="N67" s="10">
+        <v>-16.2</v>
+      </c>
+      <c r="O67" s="10">
+        <v>-44.6</v>
+      </c>
+      <c r="P67" s="9">
+        <v>1.24</v>
+      </c>
+      <c r="Q67" s="10">
+        <v>-46.3</v>
+      </c>
+    </row>
+    <row r="68" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A68" s="6">
+        <v>42856</v>
+      </c>
+      <c r="B68" s="7">
+        <v>12.1</v>
+      </c>
+      <c r="C68" s="7">
+        <v>11.7</v>
+      </c>
+      <c r="D68" s="7">
+        <v>12.3</v>
+      </c>
+      <c r="E68" s="7">
+        <v>11</v>
+      </c>
+      <c r="F68" s="10">
+        <v>-0.5</v>
+      </c>
+      <c r="G68" s="10">
+        <v>-4.0999999999999996</v>
+      </c>
+      <c r="H68" s="9">
+        <v>0.221</v>
+      </c>
+      <c r="I68" s="8">
+        <v>5.76</v>
+      </c>
+      <c r="J68" s="10">
+        <v>-48.8</v>
+      </c>
+      <c r="K68" s="9">
+        <v>1.06</v>
+      </c>
+      <c r="L68" s="10">
+        <v>-46.6</v>
+      </c>
+      <c r="M68" s="9">
+        <v>0.221</v>
+      </c>
+      <c r="N68" s="8">
+        <v>5.76</v>
+      </c>
+      <c r="O68" s="10">
+        <v>-48.8</v>
+      </c>
+      <c r="P68" s="9">
+        <v>1.06</v>
+      </c>
+      <c r="Q68" s="10">
+        <v>-46.6</v>
+      </c>
+    </row>
+    <row r="69" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A69" s="6">
+        <v>42826</v>
+      </c>
+      <c r="B69" s="7">
+        <v>12.9</v>
+      </c>
+      <c r="C69" s="7">
+        <v>12.2</v>
+      </c>
+      <c r="D69" s="7">
+        <v>12.9</v>
+      </c>
+      <c r="E69" s="7">
+        <v>11.8</v>
+      </c>
+      <c r="F69" s="10">
+        <v>-0.45</v>
+      </c>
+      <c r="G69" s="10">
+        <v>-3.56</v>
+      </c>
+      <c r="H69" s="9">
+        <v>0.20899999999999999</v>
+      </c>
+      <c r="I69" s="10">
+        <v>-13.7</v>
+      </c>
+      <c r="J69" s="10">
+        <v>-39.5</v>
+      </c>
+      <c r="K69" s="9">
+        <v>0.83399999999999996</v>
+      </c>
+      <c r="L69" s="10">
+        <v>-46</v>
+      </c>
+      <c r="M69" s="9">
+        <v>0.20899999999999999</v>
+      </c>
+      <c r="N69" s="10">
+        <v>-13.7</v>
+      </c>
+      <c r="O69" s="10">
+        <v>-39.5</v>
+      </c>
+      <c r="P69" s="9">
+        <v>0.83399999999999996</v>
+      </c>
+      <c r="Q69" s="10">
+        <v>-46</v>
+      </c>
+    </row>
+    <row r="70" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A70" s="6">
+        <v>42795</v>
+      </c>
+      <c r="B70" s="7">
+        <v>12.4</v>
+      </c>
+      <c r="C70" s="7">
+        <v>12.65</v>
+      </c>
+      <c r="D70" s="7">
+        <v>14.2</v>
+      </c>
+      <c r="E70" s="7">
+        <v>12.1</v>
+      </c>
+      <c r="F70" s="8">
+        <v>0.35</v>
+      </c>
+      <c r="G70" s="8">
+        <v>2.85</v>
+      </c>
+      <c r="H70" s="9">
+        <v>0.24299999999999999</v>
+      </c>
+      <c r="I70" s="8">
+        <v>42.2</v>
+      </c>
+      <c r="J70" s="10">
+        <v>-48.6</v>
+      </c>
+      <c r="K70" s="9">
+        <v>0.624</v>
+      </c>
+      <c r="L70" s="10">
+        <v>-47.9</v>
+      </c>
+      <c r="M70" s="9">
+        <v>0.24299999999999999</v>
+      </c>
+      <c r="N70" s="8">
+        <v>42.2</v>
+      </c>
+      <c r="O70" s="10">
+        <v>-48.6</v>
+      </c>
+      <c r="P70" s="9">
+        <v>0.624</v>
+      </c>
+      <c r="Q70" s="10">
+        <v>-47.9</v>
+      </c>
+    </row>
+    <row r="71" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A71" s="6">
+        <v>42767</v>
+      </c>
+      <c r="B71" s="7">
+        <v>11.9</v>
+      </c>
+      <c r="C71" s="7">
+        <v>12.3</v>
+      </c>
+      <c r="D71" s="7">
+        <v>12.45</v>
+      </c>
+      <c r="E71" s="7">
+        <v>11.55</v>
+      </c>
+      <c r="F71" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="G71" s="8">
+        <v>4.24</v>
+      </c>
+      <c r="H71" s="9">
+        <v>0.17100000000000001</v>
+      </c>
+      <c r="I71" s="10">
+        <v>-19.100000000000001</v>
+      </c>
+      <c r="J71" s="10">
+        <v>-45.5</v>
+      </c>
+      <c r="K71" s="9">
+        <v>0.38200000000000001</v>
+      </c>
+      <c r="L71" s="10">
+        <v>-47.4</v>
+      </c>
+      <c r="M71" s="9">
+        <v>0.17100000000000001</v>
+      </c>
+      <c r="N71" s="10">
+        <v>-19.100000000000001</v>
+      </c>
+      <c r="O71" s="10">
+        <v>-45.5</v>
+      </c>
+      <c r="P71" s="9">
+        <v>0.38200000000000001</v>
+      </c>
+      <c r="Q71" s="10">
+        <v>-47.4</v>
+      </c>
+    </row>
+    <row r="72" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A72" s="6">
+        <v>42736</v>
+      </c>
+      <c r="B72" s="7">
+        <v>12.35</v>
+      </c>
+      <c r="C72" s="7">
+        <v>11.8</v>
+      </c>
+      <c r="D72" s="7">
+        <v>12.35</v>
+      </c>
+      <c r="E72" s="7">
+        <v>11.6</v>
+      </c>
+      <c r="F72" s="10">
+        <v>-0.6</v>
+      </c>
+      <c r="G72" s="10">
+        <v>-4.84</v>
+      </c>
+      <c r="H72" s="9">
+        <v>0.21099999999999999</v>
+      </c>
+      <c r="I72" s="10">
+        <v>-1.34</v>
+      </c>
+      <c r="J72" s="10">
+        <v>-48.9</v>
+      </c>
+      <c r="K72" s="9">
+        <v>0.21099999999999999</v>
+      </c>
+      <c r="L72" s="10">
+        <v>-48.9</v>
+      </c>
+      <c r="M72" s="9">
+        <v>0.21099999999999999</v>
+      </c>
+      <c r="N72" s="10">
+        <v>-1.34</v>
+      </c>
+      <c r="O72" s="10">
+        <v>-48.9</v>
+      </c>
+      <c r="P72" s="9">
+        <v>0.21099999999999999</v>
+      </c>
+      <c r="Q72" s="10">
+        <v>-48.9</v>
+      </c>
+    </row>
+    <row r="73" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A73" s="6">
+        <v>42705</v>
+      </c>
+      <c r="B73" s="7">
+        <v>12.3</v>
+      </c>
+      <c r="C73" s="7">
+        <v>12.4</v>
+      </c>
+      <c r="D73" s="7">
+        <v>12.9</v>
+      </c>
+      <c r="E73" s="7">
+        <v>12</v>
+      </c>
+      <c r="F73" s="8">
+        <v>0.1</v>
+      </c>
+      <c r="G73" s="8">
+        <v>0.81</v>
+      </c>
+      <c r="H73" s="9">
+        <v>0.214</v>
+      </c>
+      <c r="I73" s="10">
+        <v>-17.8</v>
+      </c>
+      <c r="J73" s="10">
+        <v>-56.4</v>
+      </c>
+      <c r="K73" s="9">
+        <v>4.08</v>
+      </c>
+      <c r="L73" s="10">
+        <v>-43.7</v>
+      </c>
+      <c r="M73" s="9">
+        <v>0.214</v>
+      </c>
+      <c r="N73" s="10">
+        <v>-17.8</v>
+      </c>
+      <c r="O73" s="10">
+        <v>-56.4</v>
+      </c>
+      <c r="P73" s="9">
+        <v>4.08</v>
+      </c>
+      <c r="Q73" s="10">
+        <v>-43.7</v>
+      </c>
+    </row>
+    <row r="74" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A74" s="6">
+        <v>42675</v>
+      </c>
+      <c r="B74" s="7">
+        <v>13.3</v>
+      </c>
+      <c r="C74" s="7">
+        <v>12.3</v>
+      </c>
+      <c r="D74" s="7">
+        <v>13.3</v>
+      </c>
+      <c r="E74" s="7">
+        <v>11.7</v>
+      </c>
+      <c r="F74" s="10">
+        <v>-0.95</v>
+      </c>
+      <c r="G74" s="10">
+        <v>-7.17</v>
+      </c>
+      <c r="H74" s="9">
+        <v>0.26</v>
+      </c>
+      <c r="I74" s="8">
+        <v>20.7</v>
+      </c>
+      <c r="J74" s="10">
+        <v>-46</v>
+      </c>
+      <c r="K74" s="9">
+        <v>3.86</v>
+      </c>
+      <c r="L74" s="10">
+        <v>-42.8</v>
+      </c>
+      <c r="M74" s="9">
+        <v>0.26</v>
+      </c>
+      <c r="N74" s="8">
+        <v>20.7</v>
+      </c>
+      <c r="O74" s="10">
+        <v>-46</v>
+      </c>
+      <c r="P74" s="9">
+        <v>3.86</v>
+      </c>
+      <c r="Q74" s="10">
+        <v>-42.8</v>
+      </c>
+    </row>
+    <row r="75" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A75" s="6">
+        <v>42644</v>
+      </c>
+      <c r="B75" s="7">
+        <v>11.9</v>
+      </c>
+      <c r="C75" s="7">
+        <v>13.25</v>
+      </c>
+      <c r="D75" s="7">
+        <v>13.75</v>
+      </c>
+      <c r="E75" s="7">
+        <v>11.9</v>
+      </c>
+      <c r="F75" s="8">
+        <v>1.3</v>
+      </c>
+      <c r="G75" s="8">
+        <v>10.88</v>
+      </c>
+      <c r="H75" s="9">
+        <v>0.216</v>
+      </c>
+      <c r="I75" s="10">
+        <v>-39</v>
+      </c>
+      <c r="J75" s="10">
+        <v>-53.8</v>
+      </c>
+      <c r="K75" s="9">
+        <v>3.6</v>
+      </c>
+      <c r="L75" s="10">
+        <v>-42.6</v>
+      </c>
+      <c r="M75" s="9">
+        <v>0.216</v>
+      </c>
+      <c r="N75" s="10">
+        <v>-39</v>
+      </c>
+      <c r="O75" s="10">
+        <v>-53.8</v>
+      </c>
+      <c r="P75" s="9">
+        <v>3.6</v>
+      </c>
+      <c r="Q75" s="10">
+        <v>-42.6</v>
+      </c>
+    </row>
+    <row r="76" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A76" s="6">
+        <v>42614</v>
+      </c>
+      <c r="B76" s="7">
+        <v>11.6</v>
+      </c>
+      <c r="C76" s="7">
+        <v>11.95</v>
+      </c>
+      <c r="D76" s="7">
+        <v>12.85</v>
+      </c>
+      <c r="E76" s="7">
+        <v>11.5</v>
+      </c>
+      <c r="F76" s="8">
+        <v>0.4</v>
+      </c>
+      <c r="G76" s="8">
+        <v>3.46</v>
+      </c>
+      <c r="H76" s="9">
+        <v>0.35399999999999998</v>
+      </c>
+      <c r="I76" s="10">
+        <v>-6.52</v>
+      </c>
+      <c r="J76" s="10">
+        <v>-47.3</v>
+      </c>
+      <c r="K76" s="9">
+        <v>3.39</v>
+      </c>
+      <c r="L76" s="10">
+        <v>-41.7</v>
+      </c>
+      <c r="M76" s="9">
+        <v>0.35399999999999998</v>
+      </c>
+      <c r="N76" s="10">
+        <v>-6.52</v>
+      </c>
+      <c r="O76" s="10">
+        <v>-47.3</v>
+      </c>
+      <c r="P76" s="9">
+        <v>3.39</v>
+      </c>
+      <c r="Q76" s="10">
+        <v>-41.7</v>
+      </c>
+    </row>
+    <row r="77" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A77" s="6">
+        <v>42583</v>
+      </c>
+      <c r="B77" s="7">
+        <v>12.25</v>
+      </c>
+      <c r="C77" s="7">
+        <v>11.55</v>
+      </c>
+      <c r="D77" s="7">
+        <v>12.5</v>
+      </c>
+      <c r="E77" s="7">
+        <v>10.75</v>
+      </c>
+      <c r="F77" s="10">
+        <v>-0.65</v>
+      </c>
+      <c r="G77" s="10">
+        <v>-5.33</v>
+      </c>
+      <c r="H77" s="9">
+        <v>0.378</v>
+      </c>
+      <c r="I77" s="8">
+        <v>9.93</v>
+      </c>
+      <c r="J77" s="10">
+        <v>-33.9</v>
+      </c>
+      <c r="K77" s="9">
+        <v>3.03</v>
+      </c>
+      <c r="L77" s="10">
+        <v>-40.9</v>
+      </c>
+      <c r="M77" s="9">
+        <v>0.378</v>
+      </c>
+      <c r="N77" s="8">
+        <v>9.93</v>
+      </c>
+      <c r="O77" s="10">
+        <v>-33.9</v>
+      </c>
+      <c r="P77" s="9">
+        <v>3.03</v>
+      </c>
+      <c r="Q77" s="10">
+        <v>-40.9</v>
+      </c>
+    </row>
+    <row r="78" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A78" s="6">
+        <v>42552</v>
+      </c>
+      <c r="B78" s="7">
+        <v>11.4</v>
+      </c>
+      <c r="C78" s="7">
+        <v>12.2</v>
+      </c>
+      <c r="D78" s="7">
+        <v>12.8</v>
+      </c>
+      <c r="E78" s="7">
+        <v>11.1</v>
+      </c>
+      <c r="F78" s="8">
+        <v>0.8</v>
+      </c>
+      <c r="G78" s="8">
+        <v>7.02</v>
+      </c>
+      <c r="H78" s="9">
+        <v>0.34399999999999997</v>
+      </c>
+      <c r="I78" s="8">
+        <v>2.71</v>
+      </c>
+      <c r="J78" s="10">
+        <v>-36.4</v>
+      </c>
+      <c r="K78" s="9">
+        <v>2.66</v>
+      </c>
+      <c r="L78" s="10">
+        <v>-41.8</v>
+      </c>
+      <c r="M78" s="9">
+        <v>0.34399999999999997</v>
+      </c>
+      <c r="N78" s="8">
+        <v>2.71</v>
+      </c>
+      <c r="O78" s="10">
+        <v>-36.4</v>
+      </c>
+      <c r="P78" s="9">
+        <v>2.66</v>
+      </c>
+      <c r="Q78" s="10">
+        <v>-41.8</v>
+      </c>
+    </row>
+    <row r="79" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A79" s="6">
+        <v>42522</v>
+      </c>
+      <c r="B79" s="7">
+        <v>10.25</v>
+      </c>
+      <c r="C79" s="7">
+        <v>11.4</v>
+      </c>
+      <c r="D79" s="7">
+        <v>11.75</v>
+      </c>
+      <c r="E79" s="7">
+        <v>10</v>
+      </c>
+      <c r="F79" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="G79" s="8">
+        <v>10.68</v>
+      </c>
+      <c r="H79" s="9">
+        <v>0.33500000000000002</v>
+      </c>
+      <c r="I79" s="10">
+        <v>-22.5</v>
+      </c>
+      <c r="J79" s="10">
+        <v>-42.9</v>
+      </c>
+      <c r="K79" s="9">
+        <v>2.31</v>
+      </c>
+      <c r="L79" s="10">
+        <v>-42.5</v>
+      </c>
+      <c r="M79" s="9">
+        <v>0.33500000000000002</v>
+      </c>
+      <c r="N79" s="10">
+        <v>-22.5</v>
+      </c>
+      <c r="O79" s="10">
+        <v>-42.9</v>
+      </c>
+      <c r="P79" s="9">
+        <v>2.31</v>
+      </c>
+      <c r="Q79" s="10">
+        <v>-42.5</v>
+      </c>
+    </row>
+    <row r="80" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A80" s="6">
+        <v>42491</v>
+      </c>
+      <c r="B80" s="7">
+        <v>11.35</v>
+      </c>
+      <c r="C80" s="7">
+        <v>10.3</v>
+      </c>
+      <c r="D80" s="7">
+        <v>11.35</v>
+      </c>
+      <c r="E80" s="7">
+        <v>9.8000000000000007</v>
+      </c>
+      <c r="F80" s="10">
+        <v>-0.9</v>
+      </c>
+      <c r="G80" s="10">
+        <v>-8.0399999999999991</v>
+      </c>
+      <c r="H80" s="9">
+        <v>0.433</v>
+      </c>
+      <c r="I80" s="8">
+        <v>25.1</v>
+      </c>
+      <c r="J80" s="10">
+        <v>-26.6</v>
+      </c>
+      <c r="K80" s="9">
+        <v>1.98</v>
+      </c>
+      <c r="L80" s="10">
+        <v>-42.5</v>
+      </c>
+      <c r="M80" s="9">
+        <v>0.433</v>
+      </c>
+      <c r="N80" s="8">
+        <v>25.1</v>
+      </c>
+      <c r="O80" s="10">
+        <v>-26.6</v>
+      </c>
+      <c r="P80" s="9">
+        <v>1.98</v>
+      </c>
+      <c r="Q80" s="10">
+        <v>-42.5</v>
+      </c>
+    </row>
+    <row r="81" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A81" s="6">
+        <v>42461</v>
+      </c>
+      <c r="B81" s="7">
+        <v>11.8</v>
+      </c>
+      <c r="C81" s="7">
+        <v>11.2</v>
+      </c>
+      <c r="D81" s="7">
+        <v>11.8</v>
+      </c>
+      <c r="E81" s="7">
+        <v>10.95</v>
+      </c>
+      <c r="F81" s="10">
+        <v>-0.6</v>
+      </c>
+      <c r="G81" s="10">
+        <v>-5.08</v>
+      </c>
+      <c r="H81" s="9">
+        <v>0.34599999999999997</v>
+      </c>
+      <c r="I81" s="10">
+        <v>-26.8</v>
+      </c>
+      <c r="J81" s="10">
+        <v>-42.2</v>
+      </c>
+      <c r="K81" s="9">
+        <v>1.54</v>
+      </c>
+      <c r="L81" s="10">
+        <v>-45.8</v>
+      </c>
+      <c r="M81" s="9">
+        <v>0.34599999999999997</v>
+      </c>
+      <c r="N81" s="10">
+        <v>-26.8</v>
+      </c>
+      <c r="O81" s="10">
+        <v>-42.2</v>
+      </c>
+      <c r="P81" s="9">
+        <v>1.54</v>
+      </c>
+      <c r="Q81" s="10">
+        <v>-45.8</v>
+      </c>
+    </row>
+    <row r="82" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A82" s="6">
+        <v>42430</v>
+      </c>
+      <c r="B82" s="7">
+        <v>11.7</v>
+      </c>
+      <c r="C82" s="7">
+        <v>11.8</v>
+      </c>
+      <c r="D82" s="7">
+        <v>13.55</v>
+      </c>
+      <c r="E82" s="7">
+        <v>11.65</v>
+      </c>
+      <c r="F82" s="8">
+        <v>0.1</v>
+      </c>
+      <c r="G82" s="8">
+        <v>0.85</v>
+      </c>
+      <c r="H82" s="9">
+        <v>0.47299999999999998</v>
+      </c>
+      <c r="I82" s="8">
+        <v>51</v>
+      </c>
+      <c r="J82" s="10">
+        <v>-31.5</v>
+      </c>
+      <c r="K82" s="9">
+        <v>1.2</v>
+      </c>
+      <c r="L82" s="10">
+        <v>-46.7</v>
+      </c>
+      <c r="M82" s="9">
+        <v>0.47299999999999998</v>
+      </c>
+      <c r="N82" s="8">
+        <v>51</v>
+      </c>
+      <c r="O82" s="10">
+        <v>-31.5</v>
+      </c>
+      <c r="P82" s="9">
+        <v>1.2</v>
+      </c>
+      <c r="Q82" s="10">
+        <v>-46.7</v>
+      </c>
+    </row>
+    <row r="83" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A83" s="6">
+        <v>42401</v>
+      </c>
+      <c r="B83" s="7">
+        <v>11.55</v>
+      </c>
+      <c r="C83" s="7">
+        <v>11.7</v>
+      </c>
+      <c r="D83" s="7">
+        <v>12.1</v>
+      </c>
+      <c r="E83" s="7">
+        <v>11.25</v>
+      </c>
+      <c r="F83" s="8">
+        <v>0.15</v>
+      </c>
+      <c r="G83" s="8">
+        <v>1.3</v>
+      </c>
+      <c r="H83" s="9">
+        <v>0.313</v>
+      </c>
+      <c r="I83" s="10">
+        <v>-24.1</v>
+      </c>
+      <c r="J83" s="10">
+        <v>-50.6</v>
+      </c>
+      <c r="K83" s="9">
+        <v>0.72599999999999998</v>
+      </c>
+      <c r="L83" s="10">
+        <v>-53.4</v>
+      </c>
+      <c r="M83" s="9">
+        <v>0.313</v>
+      </c>
+      <c r="N83" s="10">
+        <v>-24.1</v>
+      </c>
+      <c r="O83" s="10">
+        <v>-50.6</v>
+      </c>
+      <c r="P83" s="9">
+        <v>0.72599999999999998</v>
+      </c>
+      <c r="Q83" s="10">
+        <v>-53.4</v>
+      </c>
+    </row>
+    <row r="84" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A84" s="6">
+        <v>42370</v>
+      </c>
+      <c r="B84" s="7">
+        <v>13.2</v>
+      </c>
+      <c r="C84" s="7">
+        <v>11.55</v>
+      </c>
+      <c r="D84" s="7">
+        <v>13.35</v>
+      </c>
+      <c r="E84" s="7">
+        <v>10.8</v>
+      </c>
+      <c r="F84" s="10">
+        <v>-1.65</v>
+      </c>
+      <c r="G84" s="10">
+        <v>-12.5</v>
+      </c>
+      <c r="H84" s="9">
+        <v>0.41299999999999998</v>
+      </c>
+      <c r="I84" s="10">
+        <v>-15.9</v>
+      </c>
+      <c r="J84" s="10">
+        <v>-55.4</v>
+      </c>
+      <c r="K84" s="9">
+        <v>0.41299999999999998</v>
+      </c>
+      <c r="L84" s="10">
+        <v>-55.4</v>
+      </c>
+      <c r="M84" s="9">
+        <v>0.41299999999999998</v>
+      </c>
+      <c r="N84" s="10">
+        <v>-15.9</v>
+      </c>
+      <c r="O84" s="10">
+        <v>-55.4</v>
+      </c>
+      <c r="P84" s="9">
+        <v>0.41299999999999998</v>
+      </c>
+      <c r="Q84" s="10">
+        <v>-55.4</v>
+      </c>
+    </row>
+    <row r="85" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A85" s="6">
+        <v>42339</v>
+      </c>
+      <c r="B85" s="7">
+        <v>13.75</v>
+      </c>
+      <c r="C85" s="7">
+        <v>13.2</v>
+      </c>
+      <c r="D85" s="7">
+        <v>14.4</v>
+      </c>
+      <c r="E85" s="7">
+        <v>12.95</v>
+      </c>
+      <c r="F85" s="10">
+        <v>-0.55000000000000004</v>
+      </c>
+      <c r="G85" s="10">
+        <v>-4</v>
+      </c>
+      <c r="H85" s="9">
+        <v>0.49099999999999999</v>
+      </c>
+      <c r="I85" s="8">
+        <v>1.77</v>
+      </c>
+      <c r="J85" s="10">
+        <v>-51.5</v>
+      </c>
+      <c r="K85" s="9">
+        <v>7.25</v>
+      </c>
+      <c r="L85" s="10">
+        <v>-45.5</v>
+      </c>
+      <c r="M85" s="9">
+        <v>0.49099999999999999</v>
+      </c>
+      <c r="N85" s="8">
+        <v>1.77</v>
+      </c>
+      <c r="O85" s="10">
+        <v>-51.5</v>
+      </c>
+      <c r="P85" s="9">
+        <v>7.25</v>
+      </c>
+      <c r="Q85" s="10">
+        <v>-45.5</v>
+      </c>
+    </row>
+    <row r="86" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A86" s="6">
+        <v>42309</v>
+      </c>
+      <c r="B86" s="7">
+        <v>13.3</v>
+      </c>
+      <c r="C86" s="7">
+        <v>13.75</v>
+      </c>
+      <c r="D86" s="7">
+        <v>14.6</v>
+      </c>
+      <c r="E86" s="7">
+        <v>13</v>
+      </c>
+      <c r="F86" s="8">
+        <v>0.35</v>
+      </c>
+      <c r="G86" s="8">
+        <v>2.61</v>
+      </c>
+      <c r="H86" s="9">
+        <v>0.48199999999999998</v>
+      </c>
+      <c r="I86" s="8">
+        <v>3.38</v>
+      </c>
+      <c r="J86" s="10">
+        <v>-70</v>
+      </c>
+      <c r="K86" s="9">
+        <v>6.76</v>
+      </c>
+      <c r="L86" s="10">
+        <v>-45</v>
+      </c>
+      <c r="M86" s="9">
+        <v>0.48199999999999998</v>
+      </c>
+      <c r="N86" s="8">
+        <v>3.38</v>
+      </c>
+      <c r="O86" s="10">
+        <v>-70</v>
+      </c>
+      <c r="P86" s="9">
+        <v>6.76</v>
+      </c>
+      <c r="Q86" s="10">
+        <v>-45</v>
+      </c>
+    </row>
+    <row r="87" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A87" s="6">
+        <v>42278</v>
+      </c>
+      <c r="B87" s="7">
+        <v>12.5</v>
+      </c>
+      <c r="C87" s="7">
+        <v>13.4</v>
+      </c>
+      <c r="D87" s="7">
+        <v>14.7</v>
+      </c>
+      <c r="E87" s="7">
+        <v>12.5</v>
+      </c>
+      <c r="F87" s="8">
+        <v>1</v>
+      </c>
+      <c r="G87" s="8">
+        <v>8.06</v>
+      </c>
+      <c r="H87" s="9">
+        <v>0.46600000000000003</v>
+      </c>
+      <c r="I87" s="10">
+        <v>-30.5</v>
+      </c>
+      <c r="J87" s="10">
+        <v>-57.9</v>
+      </c>
+      <c r="K87" s="9">
+        <v>6.27</v>
+      </c>
+      <c r="L87" s="10">
+        <v>-41.3</v>
+      </c>
+      <c r="M87" s="9">
+        <v>0.46600000000000003</v>
+      </c>
+      <c r="N87" s="10">
+        <v>-30.5</v>
+      </c>
+      <c r="O87" s="10">
+        <v>-57.9</v>
+      </c>
+      <c r="P87" s="9">
+        <v>6.27</v>
+      </c>
+      <c r="Q87" s="10">
+        <v>-41.3</v>
+      </c>
+    </row>
+    <row r="88" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A88" s="6">
+        <v>42248</v>
+      </c>
+      <c r="B88" s="7">
+        <v>11.8</v>
+      </c>
+      <c r="C88" s="7">
+        <v>12.4</v>
+      </c>
+      <c r="D88" s="7">
+        <v>14.5</v>
+      </c>
+      <c r="E88" s="7">
+        <v>11.75</v>
+      </c>
+      <c r="F88" s="8">
+        <v>0.35</v>
+      </c>
+      <c r="G88" s="8">
+        <v>2.9</v>
+      </c>
+      <c r="H88" s="9">
+        <v>0.67100000000000004</v>
+      </c>
+      <c r="I88" s="8">
+        <v>17.2</v>
+      </c>
+      <c r="J88" s="10">
+        <v>-48.8</v>
+      </c>
+      <c r="K88" s="9">
+        <v>5.81</v>
+      </c>
+      <c r="L88" s="10">
+        <v>-39.299999999999997</v>
+      </c>
+      <c r="M88" s="9">
+        <v>0.67100000000000004</v>
+      </c>
+      <c r="N88" s="8">
+        <v>17.2</v>
+      </c>
+      <c r="O88" s="10">
+        <v>-48.8</v>
+      </c>
+      <c r="P88" s="9">
+        <v>5.81</v>
+      </c>
+      <c r="Q88" s="10">
+        <v>-39.299999999999997</v>
+      </c>
+    </row>
+    <row r="89" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A89" s="6">
+        <v>42217</v>
+      </c>
+      <c r="B89" s="7">
+        <v>12.35</v>
+      </c>
+      <c r="C89" s="7">
+        <v>12.05</v>
+      </c>
+      <c r="D89" s="7">
+        <v>12.9</v>
+      </c>
+      <c r="E89" s="7">
+        <v>9.76</v>
+      </c>
+      <c r="F89" s="10">
+        <v>-0.55000000000000004</v>
+      </c>
+      <c r="G89" s="10">
+        <v>-4.37</v>
+      </c>
+      <c r="H89" s="9">
+        <v>0.57299999999999995</v>
+      </c>
+      <c r="I89" s="8">
+        <v>5.86</v>
+      </c>
+      <c r="J89" s="10">
+        <v>-49</v>
+      </c>
+      <c r="K89" s="9">
+        <v>5.14</v>
+      </c>
+      <c r="L89" s="10">
+        <v>-37.799999999999997</v>
+      </c>
+      <c r="M89" s="9">
+        <v>0.57299999999999995</v>
+      </c>
+      <c r="N89" s="8">
+        <v>5.86</v>
+      </c>
+      <c r="O89" s="10">
+        <v>-49</v>
+      </c>
+      <c r="P89" s="9">
+        <v>5.14</v>
+      </c>
+      <c r="Q89" s="10">
+        <v>-37.799999999999997</v>
+      </c>
+    </row>
+    <row r="90" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A90" s="6">
+        <v>42186</v>
+      </c>
+      <c r="B90" s="7">
+        <v>15.55</v>
+      </c>
+      <c r="C90" s="7">
+        <v>12.6</v>
+      </c>
+      <c r="D90" s="7">
+        <v>17.100000000000001</v>
+      </c>
+      <c r="E90" s="7">
+        <v>11.95</v>
+      </c>
+      <c r="F90" s="10">
+        <v>-2.95</v>
+      </c>
+      <c r="G90" s="10">
+        <v>-18.97</v>
+      </c>
+      <c r="H90" s="9">
+        <v>0.54100000000000004</v>
+      </c>
+      <c r="I90" s="10">
+        <v>-7.79</v>
+      </c>
+      <c r="J90" s="10">
+        <v>-48.4</v>
+      </c>
+      <c r="K90" s="9">
+        <v>4.5599999999999996</v>
+      </c>
+      <c r="L90" s="10">
+        <v>-36.1</v>
+      </c>
+      <c r="M90" s="9">
+        <v>0.54100000000000004</v>
+      </c>
+      <c r="N90" s="10">
+        <v>-7.79</v>
+      </c>
+      <c r="O90" s="10">
+        <v>-48.4</v>
+      </c>
+      <c r="P90" s="9">
+        <v>4.5599999999999996</v>
+      </c>
+      <c r="Q90" s="10">
+        <v>-36.1</v>
+      </c>
+    </row>
+    <row r="91" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A91" s="6">
+        <v>42156</v>
+      </c>
+      <c r="B91" s="7">
+        <v>16.7</v>
+      </c>
+      <c r="C91" s="7">
+        <v>15.55</v>
+      </c>
+      <c r="D91" s="7">
+        <v>16.7</v>
+      </c>
+      <c r="E91" s="7">
+        <v>13.05</v>
+      </c>
+      <c r="F91" s="10">
+        <v>-1.1000000000000001</v>
+      </c>
+      <c r="G91" s="10">
+        <v>-6.61</v>
+      </c>
+      <c r="H91" s="9">
+        <v>0.58699999999999997</v>
+      </c>
+      <c r="I91" s="10">
+        <v>-0.45</v>
+      </c>
+      <c r="J91" s="10">
+        <v>-47.1</v>
+      </c>
+      <c r="K91" s="9">
+        <v>4.0199999999999996</v>
+      </c>
+      <c r="L91" s="10">
+        <v>-34</v>
+      </c>
+      <c r="M91" s="9">
+        <v>0.58699999999999997</v>
+      </c>
+      <c r="N91" s="10">
+        <v>-0.45</v>
+      </c>
+      <c r="O91" s="10">
+        <v>-47.1</v>
+      </c>
+      <c r="P91" s="9">
+        <v>4.0199999999999996</v>
+      </c>
+      <c r="Q91" s="10">
+        <v>-34</v>
+      </c>
+    </row>
+    <row r="92" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A92" s="6">
+        <v>42125</v>
+      </c>
+      <c r="B92" s="7">
+        <v>18.899999999999999</v>
+      </c>
+      <c r="C92" s="7">
+        <v>16.649999999999999</v>
+      </c>
+      <c r="D92" s="7">
+        <v>19.149999999999999</v>
+      </c>
+      <c r="E92" s="7">
+        <v>15</v>
+      </c>
+      <c r="F92" s="10">
+        <v>-2.0499999999999998</v>
+      </c>
+      <c r="G92" s="10">
+        <v>-10.96</v>
+      </c>
+      <c r="H92" s="9">
+        <v>0.58899999999999997</v>
+      </c>
+      <c r="I92" s="10">
+        <v>-1.4</v>
+      </c>
+      <c r="J92" s="10">
+        <v>-50.9</v>
+      </c>
+      <c r="K92" s="9">
+        <v>3.44</v>
+      </c>
+      <c r="L92" s="10">
+        <v>-31</v>
+      </c>
+      <c r="M92" s="9">
+        <v>0.58899999999999997</v>
+      </c>
+      <c r="N92" s="10">
+        <v>-1.4</v>
+      </c>
+      <c r="O92" s="10">
+        <v>-50.9</v>
+      </c>
+      <c r="P92" s="9">
+        <v>3.44</v>
+      </c>
+      <c r="Q92" s="10">
+        <v>-31</v>
+      </c>
+    </row>
+    <row r="93" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A93" s="6">
+        <v>42095</v>
+      </c>
+      <c r="B93" s="7">
+        <v>24.6</v>
+      </c>
+      <c r="C93" s="7">
+        <v>18.7</v>
+      </c>
+      <c r="D93" s="7">
+        <v>25.2</v>
+      </c>
+      <c r="E93" s="7">
+        <v>18.55</v>
+      </c>
+      <c r="F93" s="10">
+        <v>-6.15</v>
+      </c>
+      <c r="G93" s="10">
+        <v>-24.75</v>
+      </c>
+      <c r="H93" s="9">
+        <v>0.59799999999999998</v>
+      </c>
+      <c r="I93" s="10">
+        <v>-13.4</v>
+      </c>
+      <c r="J93" s="10">
+        <v>-45</v>
+      </c>
+      <c r="K93" s="9">
+        <v>2.85</v>
+      </c>
+      <c r="L93" s="10">
+        <v>-24.7</v>
+      </c>
+      <c r="M93" s="9">
+        <v>0.59799999999999998</v>
+      </c>
+      <c r="N93" s="10">
+        <v>-13.4</v>
+      </c>
+      <c r="O93" s="10">
+        <v>-45</v>
+      </c>
+      <c r="P93" s="9">
+        <v>2.85</v>
+      </c>
+      <c r="Q93" s="10">
+        <v>-24.7</v>
+      </c>
+    </row>
+    <row r="94" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A94" s="6">
+        <v>42064</v>
+      </c>
+      <c r="B94" s="7">
+        <v>24.75</v>
+      </c>
+      <c r="C94" s="7">
+        <v>24.85</v>
+      </c>
+      <c r="D94" s="7">
+        <v>26.2</v>
+      </c>
+      <c r="E94" s="7">
+        <v>23.85</v>
+      </c>
+      <c r="F94" s="8">
+        <v>0.35</v>
+      </c>
+      <c r="G94" s="8">
+        <v>1.43</v>
+      </c>
+      <c r="H94" s="9">
+        <v>0.69</v>
+      </c>
+      <c r="I94" s="8">
+        <v>8.9499999999999993</v>
+      </c>
+      <c r="J94" s="10">
+        <v>-33.299999999999997</v>
+      </c>
+      <c r="K94" s="9">
+        <v>2.25</v>
+      </c>
+      <c r="L94" s="10">
+        <v>-16.600000000000001</v>
+      </c>
+      <c r="M94" s="9">
+        <v>0.69</v>
+      </c>
+      <c r="N94" s="8">
+        <v>8.9499999999999993</v>
+      </c>
+      <c r="O94" s="10">
+        <v>-33.299999999999997</v>
+      </c>
+      <c r="P94" s="9">
+        <v>2.25</v>
+      </c>
+      <c r="Q94" s="10">
+        <v>-16.600000000000001</v>
+      </c>
+    </row>
+    <row r="95" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A95" s="6">
+        <v>42036</v>
+      </c>
+      <c r="B95" s="7">
+        <v>26.1</v>
+      </c>
+      <c r="C95" s="7">
+        <v>24.5</v>
+      </c>
+      <c r="D95" s="7">
+        <v>26.3</v>
+      </c>
+      <c r="E95" s="7">
+        <v>23.3</v>
+      </c>
+      <c r="F95" s="10">
+        <v>-1.4</v>
+      </c>
+      <c r="G95" s="10">
+        <v>-5.41</v>
+      </c>
+      <c r="H95" s="9">
+        <v>0.63400000000000001</v>
+      </c>
+      <c r="I95" s="10">
+        <v>-31.5</v>
+      </c>
+      <c r="J95" s="10">
+        <v>-16.2</v>
+      </c>
+      <c r="K95" s="9">
+        <v>1.56</v>
+      </c>
+      <c r="L95" s="10">
+        <v>-6.08</v>
+      </c>
+      <c r="M95" s="9">
+        <v>0.63400000000000001</v>
+      </c>
+      <c r="N95" s="10">
+        <v>-31.5</v>
+      </c>
+      <c r="O95" s="10">
+        <v>-16.2</v>
+      </c>
+      <c r="P95" s="9">
+        <v>1.56</v>
+      </c>
+      <c r="Q95" s="10">
+        <v>-6.08</v>
+      </c>
+    </row>
+    <row r="96" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A96" s="6">
+        <v>42005</v>
+      </c>
+      <c r="B96" s="7">
+        <v>26.9</v>
+      </c>
+      <c r="C96" s="7">
+        <v>25.9</v>
+      </c>
+      <c r="D96" s="7">
+        <v>28.2</v>
+      </c>
+      <c r="E96" s="7">
+        <v>24.15</v>
+      </c>
+      <c r="F96" s="10">
+        <v>-0.8</v>
+      </c>
+      <c r="G96" s="10">
+        <v>-3</v>
+      </c>
+      <c r="H96" s="9">
+        <v>0.92600000000000005</v>
+      </c>
+      <c r="I96" s="10">
+        <v>-8.49</v>
+      </c>
+      <c r="J96" s="8">
+        <v>2.39</v>
+      </c>
+      <c r="K96" s="9">
+        <v>0.92600000000000005</v>
+      </c>
+      <c r="L96" s="8">
+        <v>2.39</v>
+      </c>
+      <c r="M96" s="9">
+        <v>0.92600000000000005</v>
+      </c>
+      <c r="N96" s="10">
+        <v>-8.49</v>
+      </c>
+      <c r="O96" s="8">
+        <v>2.39</v>
+      </c>
+      <c r="P96" s="9">
+        <v>0.92600000000000005</v>
+      </c>
+      <c r="Q96" s="8">
+        <v>2.39</v>
+      </c>
+    </row>
+    <row r="97" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A97" s="6">
+        <v>41974</v>
+      </c>
+      <c r="B97" s="7">
+        <v>23.5</v>
+      </c>
+      <c r="C97" s="7">
+        <v>26.7</v>
+      </c>
+      <c r="D97" s="7">
+        <v>29.4</v>
+      </c>
+      <c r="E97" s="7">
+        <v>23.5</v>
+      </c>
+      <c r="F97" s="8">
+        <v>2.7</v>
+      </c>
+      <c r="G97" s="8">
+        <v>11.25</v>
+      </c>
+      <c r="H97" s="9">
+        <v>1.01</v>
+      </c>
+      <c r="I97" s="10">
+        <v>-37</v>
+      </c>
+      <c r="J97" s="10">
+        <v>-1.1499999999999999</v>
+      </c>
+      <c r="K97" s="9">
+        <v>13.3</v>
+      </c>
+      <c r="L97" s="8">
+        <v>6.2</v>
+      </c>
+      <c r="M97" s="9">
+        <v>1.01</v>
+      </c>
+      <c r="N97" s="10">
+        <v>-37</v>
+      </c>
+      <c r="O97" s="10">
+        <v>-1.1499999999999999</v>
+      </c>
+      <c r="P97" s="9">
+        <v>13.3</v>
+      </c>
+      <c r="Q97" s="8">
+        <v>6.2</v>
+      </c>
+    </row>
+    <row r="98" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A98" s="6">
+        <v>41944</v>
+      </c>
+      <c r="B98" s="7">
+        <v>22</v>
+      </c>
+      <c r="C98" s="7">
+        <v>24</v>
+      </c>
+      <c r="D98" s="7">
+        <v>24.25</v>
+      </c>
+      <c r="E98" s="7">
+        <v>18.5</v>
+      </c>
+      <c r="F98" s="8">
+        <v>1.7</v>
+      </c>
+      <c r="G98" s="8">
+        <v>7.62</v>
+      </c>
+      <c r="H98" s="9">
+        <v>1.61</v>
+      </c>
+      <c r="I98" s="8">
+        <v>45.1</v>
+      </c>
+      <c r="J98" s="8">
+        <v>23.6</v>
+      </c>
+      <c r="K98" s="9">
+        <v>12.29</v>
+      </c>
+      <c r="L98" s="8">
+        <v>6.86</v>
+      </c>
+      <c r="M98" s="9">
+        <v>1.61</v>
+      </c>
+      <c r="N98" s="8">
+        <v>45.1</v>
+      </c>
+      <c r="O98" s="8">
+        <v>23.6</v>
+      </c>
+      <c r="P98" s="9">
+        <v>12.29</v>
+      </c>
+      <c r="Q98" s="8">
+        <v>6.86</v>
+      </c>
+    </row>
+    <row r="99" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A99" s="6">
+        <v>41913</v>
+      </c>
+      <c r="B99" s="7">
+        <v>21.8</v>
+      </c>
+      <c r="C99" s="7">
+        <v>22.3</v>
+      </c>
+      <c r="D99" s="7">
+        <v>29.05</v>
+      </c>
+      <c r="E99" s="7">
+        <v>19.5</v>
+      </c>
+      <c r="F99" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="G99" s="8">
+        <v>2.29</v>
+      </c>
+      <c r="H99" s="9">
+        <v>1.1100000000000001</v>
+      </c>
+      <c r="I99" s="10">
+        <v>-15.4</v>
+      </c>
+      <c r="J99" s="8">
+        <v>2.75</v>
+      </c>
+      <c r="K99" s="9">
+        <v>10.68</v>
+      </c>
+      <c r="L99" s="8">
+        <v>4.72</v>
+      </c>
+      <c r="M99" s="9">
+        <v>1.1100000000000001</v>
+      </c>
+      <c r="N99" s="10">
+        <v>-15.4</v>
+      </c>
+      <c r="O99" s="8">
+        <v>2.75</v>
+      </c>
+      <c r="P99" s="9">
+        <v>10.68</v>
+      </c>
+      <c r="Q99" s="8">
+        <v>4.72</v>
+      </c>
+    </row>
+    <row r="100" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A100" s="6">
+        <v>41883</v>
+      </c>
+      <c r="B100" s="7">
+        <v>18.649999999999999</v>
+      </c>
+      <c r="C100" s="7">
+        <v>21.8</v>
+      </c>
+      <c r="D100" s="7">
+        <v>23.65</v>
+      </c>
+      <c r="E100" s="7">
+        <v>16.8</v>
+      </c>
+      <c r="F100" s="8">
+        <v>3.4</v>
+      </c>
+      <c r="G100" s="8">
+        <v>18.48</v>
+      </c>
+      <c r="H100" s="9">
+        <v>1.31</v>
+      </c>
+      <c r="I100" s="8">
+        <v>16.5</v>
+      </c>
+      <c r="J100" s="8">
+        <v>15</v>
+      </c>
+      <c r="K100" s="9">
+        <v>9.57</v>
+      </c>
+      <c r="L100" s="8">
+        <v>4.95</v>
+      </c>
+      <c r="M100" s="9">
+        <v>1.31</v>
+      </c>
+      <c r="N100" s="8">
+        <v>16.5</v>
+      </c>
+      <c r="O100" s="8">
+        <v>15</v>
+      </c>
+      <c r="P100" s="9">
+        <v>9.57</v>
+      </c>
+      <c r="Q100" s="8">
+        <v>4.95</v>
+      </c>
+    </row>
+    <row r="101" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A101" s="6">
+        <v>41852</v>
+      </c>
+      <c r="B101" s="7">
+        <v>15.65</v>
+      </c>
+      <c r="C101" s="7">
+        <v>18.399999999999999</v>
+      </c>
+      <c r="D101" s="7">
+        <v>18.8</v>
+      </c>
+      <c r="E101" s="7">
+        <v>15</v>
+      </c>
+      <c r="F101" s="8">
+        <v>2.75</v>
+      </c>
+      <c r="G101" s="8">
+        <v>17.57</v>
+      </c>
+      <c r="H101" s="9">
+        <v>1.1200000000000001</v>
+      </c>
+      <c r="I101" s="8">
+        <v>7.2</v>
+      </c>
+      <c r="J101" s="8">
+        <v>11.6</v>
+      </c>
+      <c r="K101" s="9">
+        <v>8.26</v>
+      </c>
+      <c r="L101" s="8">
+        <v>3.51</v>
+      </c>
+      <c r="M101" s="9">
+        <v>1.1200000000000001</v>
+      </c>
+      <c r="N101" s="8">
+        <v>7.2</v>
+      </c>
+      <c r="O101" s="8">
+        <v>11.6</v>
+      </c>
+      <c r="P101" s="9">
+        <v>8.26</v>
+      </c>
+      <c r="Q101" s="8">
+        <v>3.51</v>
+      </c>
+    </row>
+    <row r="102" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A102" s="6">
+        <v>41821</v>
+      </c>
+      <c r="B102" s="7">
+        <v>15.1</v>
+      </c>
+      <c r="C102" s="7">
+        <v>15.65</v>
+      </c>
+      <c r="D102" s="7">
+        <v>17.850000000000001</v>
+      </c>
+      <c r="E102" s="7">
+        <v>15</v>
+      </c>
+      <c r="F102" s="8">
+        <v>0.45</v>
+      </c>
+      <c r="G102" s="8">
+        <v>2.96</v>
+      </c>
+      <c r="H102" s="9">
+        <v>1.05</v>
+      </c>
+      <c r="I102" s="10">
+        <v>-5.45</v>
+      </c>
+      <c r="J102" s="8">
+        <v>5.68</v>
+      </c>
+      <c r="K102" s="9">
+        <v>7.14</v>
+      </c>
+      <c r="L102" s="8">
+        <v>2.34</v>
+      </c>
+      <c r="M102" s="9">
+        <v>1.05</v>
+      </c>
+      <c r="N102" s="10">
+        <v>-5.45</v>
+      </c>
+      <c r="O102" s="8">
+        <v>5.68</v>
+      </c>
+      <c r="P102" s="9">
+        <v>7.14</v>
+      </c>
+      <c r="Q102" s="8">
+        <v>2.34</v>
+      </c>
+    </row>
+    <row r="103" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A103" s="6">
+        <v>41791</v>
+      </c>
+      <c r="B103" s="7">
+        <v>15.7</v>
+      </c>
+      <c r="C103" s="7">
+        <v>15.2</v>
+      </c>
+      <c r="D103" s="7">
+        <v>16.600000000000001</v>
+      </c>
+      <c r="E103" s="7">
+        <v>14.7</v>
+      </c>
+      <c r="F103" s="10">
+        <v>-0.55000000000000004</v>
+      </c>
+      <c r="G103" s="10">
+        <v>-3.49</v>
+      </c>
+      <c r="H103" s="9">
+        <v>1.1100000000000001</v>
+      </c>
+      <c r="I103" s="10">
+        <v>-7.69</v>
+      </c>
+      <c r="J103" s="8">
+        <v>7.61</v>
+      </c>
+      <c r="K103" s="9">
+        <v>6.09</v>
+      </c>
+      <c r="L103" s="8">
+        <v>1.79</v>
+      </c>
+      <c r="M103" s="9">
+        <v>1.1100000000000001</v>
+      </c>
+      <c r="N103" s="10">
+        <v>-7.69</v>
+      </c>
+      <c r="O103" s="8">
+        <v>7.61</v>
+      </c>
+      <c r="P103" s="9">
+        <v>6.09</v>
+      </c>
+      <c r="Q103" s="8">
+        <v>1.79</v>
+      </c>
+    </row>
+    <row r="104" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A104" s="6">
+        <v>41760</v>
+      </c>
+      <c r="B104" s="7">
+        <v>13.5</v>
+      </c>
+      <c r="C104" s="7">
+        <v>15.75</v>
+      </c>
+      <c r="D104" s="7">
+        <v>16.95</v>
+      </c>
+      <c r="E104" s="7">
+        <v>13.5</v>
+      </c>
+      <c r="F104" s="8">
+        <v>2.25</v>
+      </c>
+      <c r="G104" s="8">
+        <v>16.670000000000002</v>
+      </c>
+      <c r="H104" s="9">
+        <v>1.2</v>
+      </c>
+      <c r="I104" s="8">
+        <v>10.5</v>
+      </c>
+      <c r="J104" s="8">
+        <v>9.14</v>
+      </c>
+      <c r="K104" s="9">
+        <v>4.9800000000000004</v>
+      </c>
+      <c r="L104" s="8">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="M104" s="9">
+        <v>1.2</v>
+      </c>
+      <c r="N104" s="8">
+        <v>10.5</v>
+      </c>
+      <c r="O104" s="8">
+        <v>9.14</v>
+      </c>
+      <c r="P104" s="9">
+        <v>4.9800000000000004</v>
+      </c>
+      <c r="Q104" s="8">
+        <v>0.57999999999999996</v>
+      </c>
+    </row>
+    <row r="105" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A105" s="6">
+        <v>41730</v>
+      </c>
+      <c r="B105" s="7">
+        <v>16.25</v>
+      </c>
+      <c r="C105" s="7">
+        <v>13.5</v>
+      </c>
+      <c r="D105" s="7">
+        <v>16.600000000000001</v>
+      </c>
+      <c r="E105" s="7">
+        <v>13.3</v>
+      </c>
+      <c r="F105" s="10">
+        <v>-2.6</v>
+      </c>
+      <c r="G105" s="10">
+        <v>-16.149999999999999</v>
+      </c>
+      <c r="H105" s="9">
+        <v>1.0900000000000001</v>
+      </c>
+      <c r="I105" s="8">
+        <v>4.9400000000000004</v>
+      </c>
+      <c r="J105" s="8">
+        <v>5.99</v>
+      </c>
+      <c r="K105" s="9">
+        <v>3.78</v>
+      </c>
+      <c r="L105" s="10">
+        <v>-1.86</v>
+      </c>
+      <c r="M105" s="9">
+        <v>1.0900000000000001</v>
+      </c>
+      <c r="N105" s="8">
+        <v>4.9400000000000004</v>
+      </c>
+      <c r="O105" s="8">
+        <v>5.99</v>
+      </c>
+      <c r="P105" s="9">
+        <v>3.78</v>
+      </c>
+      <c r="Q105" s="10">
+        <v>-1.86</v>
+      </c>
+    </row>
+    <row r="106" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A106" s="6">
+        <v>41699</v>
+      </c>
+      <c r="B106" s="7">
+        <v>19.3</v>
+      </c>
+      <c r="C106" s="7">
+        <v>16.100000000000001</v>
+      </c>
+      <c r="D106" s="7">
+        <v>19.399999999999999</v>
+      </c>
+      <c r="E106" s="7">
+        <v>15.3</v>
+      </c>
+      <c r="F106" s="10">
+        <v>-2.9</v>
+      </c>
+      <c r="G106" s="10">
+        <v>-15.26</v>
+      </c>
+      <c r="H106" s="9">
+        <v>1.04</v>
+      </c>
+      <c r="I106" s="8">
+        <v>36.9</v>
+      </c>
+      <c r="J106" s="10">
+        <v>-1.1000000000000001</v>
+      </c>
+      <c r="K106" s="9">
+        <v>2.7</v>
+      </c>
+      <c r="L106" s="10">
+        <v>-4.7</v>
+      </c>
+      <c r="M106" s="9">
+        <v>1.04</v>
+      </c>
+      <c r="N106" s="8">
+        <v>36.9</v>
+      </c>
+      <c r="O106" s="10">
+        <v>-1.1000000000000001</v>
+      </c>
+      <c r="P106" s="9">
+        <v>2.7</v>
+      </c>
+      <c r="Q106" s="10">
+        <v>-4.7</v>
+      </c>
+    </row>
+    <row r="107" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A107" s="6">
+        <v>41671</v>
+      </c>
+      <c r="B107" s="7">
+        <v>15.7</v>
+      </c>
+      <c r="C107" s="7">
+        <v>19</v>
+      </c>
+      <c r="D107" s="7">
+        <v>19.25</v>
+      </c>
+      <c r="E107" s="7">
+        <v>15.65</v>
+      </c>
+      <c r="F107" s="8">
+        <v>3.15</v>
+      </c>
+      <c r="G107" s="8">
+        <v>19.87</v>
+      </c>
+      <c r="H107" s="9">
+        <v>0.75600000000000001</v>
+      </c>
+      <c r="I107" s="10">
+        <v>-16.3</v>
+      </c>
+      <c r="J107" s="8">
+        <v>4.59</v>
+      </c>
+      <c r="K107" s="9">
+        <v>1.66</v>
+      </c>
+      <c r="L107" s="10">
+        <v>-6.82</v>
+      </c>
+      <c r="M107" s="9">
+        <v>0.75600000000000001</v>
+      </c>
+      <c r="N107" s="10">
+        <v>-16.3</v>
+      </c>
+      <c r="O107" s="8">
+        <v>4.59</v>
+      </c>
+      <c r="P107" s="9">
+        <v>1.66</v>
+      </c>
+      <c r="Q107" s="10">
+        <v>-6.82</v>
+      </c>
+    </row>
+    <row r="108" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A108" s="6">
+        <v>41640</v>
+      </c>
+      <c r="B108" s="7">
+        <v>15.5</v>
+      </c>
+      <c r="C108" s="7">
+        <v>15.85</v>
+      </c>
+      <c r="D108" s="7">
+        <v>18.45</v>
+      </c>
+      <c r="E108" s="7">
+        <v>15.15</v>
+      </c>
+      <c r="F108" s="8">
+        <v>0.7</v>
+      </c>
+      <c r="G108" s="8">
+        <v>4.62</v>
+      </c>
+      <c r="H108" s="9">
+        <v>0.90400000000000003</v>
+      </c>
+      <c r="I108" s="10">
+        <v>-11.7</v>
+      </c>
+      <c r="J108" s="10">
+        <v>-14.6</v>
+      </c>
+      <c r="K108" s="9">
+        <v>0.90400000000000003</v>
+      </c>
+      <c r="L108" s="10">
+        <v>-14.6</v>
+      </c>
+      <c r="M108" s="9">
+        <v>0.90400000000000003</v>
+      </c>
+      <c r="N108" s="10">
+        <v>-11.7</v>
+      </c>
+      <c r="O108" s="10">
+        <v>-14.6</v>
+      </c>
+      <c r="P108" s="9">
+        <v>0.90400000000000003</v>
+      </c>
+      <c r="Q108" s="10">
+        <v>-14.6</v>
+      </c>
+    </row>
+    <row r="109" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A109" s="6">
+        <v>41609</v>
+      </c>
+      <c r="B109" s="7">
+        <v>10.85</v>
+      </c>
+      <c r="C109" s="7">
+        <v>15.15</v>
+      </c>
+      <c r="D109" s="7">
+        <v>16.2</v>
+      </c>
+      <c r="E109" s="7">
+        <v>10.85</v>
+      </c>
+      <c r="F109" s="8">
+        <v>4.3</v>
+      </c>
+      <c r="G109" s="8">
+        <v>39.630000000000003</v>
+      </c>
+      <c r="H109" s="9">
+        <v>1.02</v>
+      </c>
+      <c r="I109" s="10">
+        <v>-21.3</v>
+      </c>
+      <c r="J109" s="8">
+        <v>15.2</v>
+      </c>
+      <c r="K109" s="9">
+        <v>12.52</v>
+      </c>
+      <c r="L109" s="8">
+        <v>43.1</v>
+      </c>
+      <c r="M109" s="9">
+        <v>1.02</v>
+      </c>
+      <c r="N109" s="10">
+        <v>-21.3</v>
+      </c>
+      <c r="O109" s="8">
+        <v>15.2</v>
+      </c>
+      <c r="P109" s="9">
+        <v>12.52</v>
+      </c>
+      <c r="Q109" s="8">
+        <v>43.1</v>
+      </c>
+    </row>
+    <row r="110" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A110" s="6">
+        <v>41579</v>
+      </c>
+      <c r="B110" s="7">
+        <v>11.6</v>
+      </c>
+      <c r="C110" s="7">
+        <v>10.85</v>
+      </c>
+      <c r="D110" s="7">
+        <v>11.65</v>
+      </c>
+      <c r="E110" s="7">
+        <v>10.65</v>
+      </c>
+      <c r="F110" s="10">
+        <v>-0.8</v>
+      </c>
+      <c r="G110" s="10">
+        <v>-6.87</v>
+      </c>
+      <c r="H110" s="9">
+        <v>1.3</v>
+      </c>
+      <c r="I110" s="8">
+        <v>20.6</v>
+      </c>
+      <c r="J110" s="8">
+        <v>61.6</v>
+      </c>
+      <c r="K110" s="9">
+        <v>11.5</v>
+      </c>
+      <c r="L110" s="8">
+        <v>46.3</v>
+      </c>
+      <c r="M110" s="9">
+        <v>1.3</v>
+      </c>
+      <c r="N110" s="8">
+        <v>20.6</v>
+      </c>
+      <c r="O110" s="8">
+        <v>61.6</v>
+      </c>
+      <c r="P110" s="9">
+        <v>11.5</v>
+      </c>
+      <c r="Q110" s="8">
+        <v>46.3</v>
+      </c>
+    </row>
+    <row r="111" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A111" s="6">
+        <v>41548</v>
+      </c>
+      <c r="B111" s="7">
+        <v>11.65</v>
+      </c>
+      <c r="C111" s="7">
+        <v>11.65</v>
+      </c>
+      <c r="D111" s="7">
+        <v>12.6</v>
+      </c>
+      <c r="E111" s="7">
+        <v>11.1</v>
+      </c>
+      <c r="F111" s="10">
+        <v>-0.1</v>
+      </c>
+      <c r="G111" s="10">
+        <v>-0.85</v>
+      </c>
+      <c r="H111" s="9">
+        <v>1.08</v>
+      </c>
+      <c r="I111" s="10">
+        <v>-5.3</v>
+      </c>
+      <c r="J111" s="8">
+        <v>25</v>
+      </c>
+      <c r="K111" s="9">
+        <v>10.199999999999999</v>
+      </c>
+      <c r="L111" s="8">
+        <v>44.5</v>
+      </c>
+      <c r="M111" s="9">
+        <v>1.08</v>
+      </c>
+      <c r="N111" s="10">
+        <v>-5.3</v>
+      </c>
+      <c r="O111" s="8">
+        <v>25</v>
+      </c>
+      <c r="P111" s="9">
+        <v>10.199999999999999</v>
+      </c>
+      <c r="Q111" s="8">
+        <v>44.5</v>
+      </c>
+    </row>
+    <row r="112" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A112" s="6">
+        <v>41518</v>
+      </c>
+      <c r="B112" s="7">
+        <v>11</v>
+      </c>
+      <c r="C112" s="7">
+        <v>11.75</v>
+      </c>
+      <c r="D112" s="7">
+        <v>12.35</v>
+      </c>
+      <c r="E112" s="7">
+        <v>10.9</v>
+      </c>
+      <c r="F112" s="8">
+        <v>0.75</v>
+      </c>
+      <c r="G112" s="8">
+        <v>6.82</v>
+      </c>
+      <c r="H112" s="9">
+        <v>1.1399999999999999</v>
+      </c>
+      <c r="I112" s="8">
+        <v>13</v>
+      </c>
+      <c r="J112" s="8">
+        <v>54.2</v>
+      </c>
+      <c r="K112" s="9">
+        <v>9.1199999999999992</v>
+      </c>
+      <c r="L112" s="8">
+        <v>47.3</v>
+      </c>
+      <c r="M112" s="9">
+        <v>1.1399999999999999</v>
+      </c>
+      <c r="N112" s="8">
+        <v>13</v>
+      </c>
+      <c r="O112" s="8">
+        <v>54.2</v>
+      </c>
+      <c r="P112" s="9">
+        <v>9.1199999999999992</v>
+      </c>
+      <c r="Q112" s="8">
+        <v>47.3</v>
+      </c>
+    </row>
+    <row r="113" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A113" s="6">
+        <v>41487</v>
+      </c>
+      <c r="B113" s="7">
+        <v>12.5</v>
+      </c>
+      <c r="C113" s="7">
+        <v>11</v>
+      </c>
+      <c r="D113" s="7">
+        <v>13.1</v>
+      </c>
+      <c r="E113" s="7">
+        <v>10.8</v>
+      </c>
+      <c r="F113" s="10">
+        <v>-1.5</v>
+      </c>
+      <c r="G113" s="10">
+        <v>-12</v>
+      </c>
+      <c r="H113" s="9">
+        <v>1.01</v>
+      </c>
+      <c r="I113" s="8">
+        <v>1.5</v>
+      </c>
+      <c r="J113" s="8">
+        <v>37.299999999999997</v>
+      </c>
+      <c r="K113" s="9">
+        <v>7.98</v>
+      </c>
+      <c r="L113" s="8">
+        <v>46.3</v>
+      </c>
+      <c r="M113" s="9">
+        <v>1.01</v>
+      </c>
+      <c r="N113" s="8">
+        <v>1.51</v>
+      </c>
+      <c r="O113" s="8">
+        <v>37.299999999999997</v>
+      </c>
+      <c r="P113" s="9">
+        <v>7.98</v>
+      </c>
+      <c r="Q113" s="8">
+        <v>46.3</v>
+      </c>
+    </row>
+    <row r="114" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A114" s="6">
+        <v>41456</v>
+      </c>
+      <c r="B114" s="7">
+        <v>12.25</v>
+      </c>
+      <c r="C114" s="7">
+        <v>12.5</v>
+      </c>
+      <c r="D114" s="7">
+        <v>13.1</v>
+      </c>
+      <c r="E114" s="7">
+        <v>11.45</v>
+      </c>
+      <c r="F114" s="8">
+        <v>0.25</v>
+      </c>
+      <c r="G114" s="8">
+        <v>2.04</v>
+      </c>
+      <c r="H114" s="9">
+        <v>0.99199999999999999</v>
+      </c>
+      <c r="I114" s="10">
+        <v>-3.71</v>
+      </c>
+      <c r="J114" s="8">
+        <v>62.7</v>
+      </c>
+      <c r="K114" s="9">
+        <v>6.98</v>
+      </c>
+      <c r="L114" s="8">
+        <v>47.7</v>
+      </c>
+      <c r="M114" s="9">
+        <v>0.99199999999999999</v>
+      </c>
+      <c r="N114" s="10">
+        <v>-3.72</v>
+      </c>
+      <c r="O114" s="8">
+        <v>62.7</v>
+      </c>
+      <c r="P114" s="9">
+        <v>6.98</v>
+      </c>
+      <c r="Q114" s="8">
+        <v>47.7</v>
+      </c>
+    </row>
+    <row r="115" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A115" s="6">
+        <v>41426</v>
+      </c>
+      <c r="B115" s="7">
+        <v>13.5</v>
+      </c>
+      <c r="C115" s="7">
+        <v>12.25</v>
+      </c>
+      <c r="D115" s="7">
+        <v>13.85</v>
+      </c>
+      <c r="E115" s="7">
+        <v>11.2</v>
+      </c>
+      <c r="F115" s="10">
+        <v>-1.45</v>
+      </c>
+      <c r="G115" s="10">
+        <v>-10.58</v>
+      </c>
+      <c r="H115" s="9">
+        <v>1.03</v>
+      </c>
+      <c r="I115" s="10">
+        <v>-6.38</v>
+      </c>
+      <c r="J115" s="8">
+        <v>78.599999999999994</v>
+      </c>
+      <c r="K115" s="9">
+        <v>5.99</v>
+      </c>
+      <c r="L115" s="8">
+        <v>45.5</v>
+      </c>
+      <c r="M115" s="9">
+        <v>1.03</v>
+      </c>
+      <c r="N115" s="10">
+        <v>-6.39</v>
+      </c>
+      <c r="O115" s="8">
+        <v>78.599999999999994</v>
+      </c>
+      <c r="P115" s="9">
+        <v>5.99</v>
+      </c>
+      <c r="Q115" s="8">
+        <v>45.5</v>
+      </c>
+    </row>
+    <row r="116" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A116" s="6">
+        <v>41395</v>
+      </c>
+      <c r="B116" s="7">
+        <v>12.8</v>
+      </c>
+      <c r="C116" s="7">
+        <v>13.7</v>
+      </c>
+      <c r="D116" s="7">
+        <v>15.4</v>
+      </c>
+      <c r="E116" s="7">
+        <v>12.8</v>
+      </c>
+      <c r="F116" s="8">
+        <v>0.9</v>
+      </c>
+      <c r="G116" s="8">
+        <v>7.03</v>
+      </c>
+      <c r="H116" s="9">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="I116" s="8">
+        <v>7.33</v>
+      </c>
+      <c r="J116" s="8">
+        <v>43.5</v>
+      </c>
+      <c r="K116" s="9">
+        <v>4.95</v>
+      </c>
+      <c r="L116" s="8">
+        <v>40.1</v>
+      </c>
+      <c r="M116" s="9">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="N116" s="8">
+        <v>7.34</v>
+      </c>
+      <c r="O116" s="8">
+        <v>43.5</v>
+      </c>
+      <c r="P116" s="9">
+        <v>4.95</v>
+      </c>
+      <c r="Q116" s="8">
+        <v>40.1</v>
+      </c>
+    </row>
+    <row r="117" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A117" s="6">
+        <v>41365</v>
+      </c>
+      <c r="B117" s="7">
+        <v>15.6</v>
+      </c>
+      <c r="C117" s="7">
+        <v>12.8</v>
+      </c>
+      <c r="D117" s="7">
+        <v>16.3</v>
+      </c>
+      <c r="E117" s="7">
+        <v>12.1</v>
+      </c>
+      <c r="F117" s="10">
+        <v>-2.6</v>
+      </c>
+      <c r="G117" s="10">
+        <v>-16.88</v>
+      </c>
+      <c r="H117" s="9">
+        <v>1.03</v>
+      </c>
+      <c r="I117" s="10">
+        <v>-2.08</v>
+      </c>
+      <c r="J117" s="8">
+        <v>38.4</v>
+      </c>
+      <c r="K117" s="9">
+        <v>3.85</v>
+      </c>
+      <c r="L117" s="8">
+        <v>39.200000000000003</v>
+      </c>
+      <c r="M117" s="9">
+        <v>1.03</v>
+      </c>
+      <c r="N117" s="10">
+        <v>-2.09</v>
+      </c>
+      <c r="O117" s="8">
+        <v>38.4</v>
+      </c>
+      <c r="P117" s="9">
+        <v>3.85</v>
+      </c>
+      <c r="Q117" s="8">
+        <v>39.200000000000003</v>
+      </c>
+    </row>
+    <row r="118" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A118" s="6">
+        <v>41334</v>
+      </c>
+      <c r="B118" s="7">
+        <v>10.65</v>
+      </c>
+      <c r="C118" s="7">
+        <v>15.4</v>
+      </c>
+      <c r="D118" s="7">
+        <v>15.4</v>
+      </c>
+      <c r="E118" s="7">
+        <v>10.4</v>
+      </c>
+      <c r="F118" s="8">
+        <v>4.8</v>
+      </c>
+      <c r="G118" s="8">
+        <v>45.28</v>
+      </c>
+      <c r="H118" s="9">
+        <v>1.05</v>
+      </c>
+      <c r="I118" s="8">
+        <v>44.8</v>
+      </c>
+      <c r="J118" s="8">
+        <v>32.200000000000003</v>
+      </c>
+      <c r="K118" s="9">
+        <v>2.83</v>
+      </c>
+      <c r="L118" s="8">
+        <v>39.4</v>
+      </c>
+      <c r="M118" s="9">
+        <v>1.05</v>
+      </c>
+      <c r="N118" s="8">
+        <v>44.8</v>
+      </c>
+      <c r="O118" s="8">
+        <v>32.200000000000003</v>
+      </c>
+      <c r="P118" s="9">
+        <v>2.83</v>
+      </c>
+      <c r="Q118" s="8">
+        <v>39.5</v>
+      </c>
+    </row>
+    <row r="119" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A119" s="6">
+        <v>41306</v>
+      </c>
+      <c r="B119" s="7">
+        <v>10.35</v>
+      </c>
+      <c r="C119" s="7">
+        <v>10.6</v>
+      </c>
+      <c r="D119" s="7">
+        <v>11</v>
+      </c>
+      <c r="E119" s="7">
+        <v>9.76</v>
+      </c>
+      <c r="F119" s="8">
+        <v>0.3</v>
+      </c>
+      <c r="G119" s="8">
+        <v>2.91</v>
+      </c>
+      <c r="H119" s="9">
+        <v>0.72299999999999998</v>
+      </c>
+      <c r="I119" s="10">
+        <v>-31.7</v>
+      </c>
+      <c r="J119" s="8">
+        <v>17</v>
+      </c>
+      <c r="K119" s="9">
+        <v>1.78</v>
+      </c>
+      <c r="L119" s="8">
+        <v>44.1</v>
+      </c>
+      <c r="M119" s="9">
+        <v>0.72299999999999998</v>
+      </c>
+      <c r="N119" s="10">
+        <v>-31.7</v>
+      </c>
+      <c r="O119" s="8">
+        <v>17</v>
+      </c>
+      <c r="P119" s="9">
+        <v>1.78</v>
+      </c>
+      <c r="Q119" s="8">
+        <v>44.1</v>
+      </c>
+    </row>
+    <row r="120" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A120" s="6">
+        <v>41275</v>
+      </c>
+      <c r="B120" s="7">
+        <v>10.9</v>
+      </c>
+      <c r="C120" s="7">
+        <v>10.3</v>
+      </c>
+      <c r="D120" s="7">
+        <v>10.9</v>
+      </c>
+      <c r="E120" s="7">
+        <v>10.1</v>
+      </c>
+      <c r="F120" s="10">
+        <v>-0.4</v>
+      </c>
+      <c r="G120" s="10">
+        <v>-3.74</v>
+      </c>
+      <c r="H120" s="9">
+        <v>1.06</v>
+      </c>
+      <c r="I120" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J120" s="8">
+        <v>71.3</v>
+      </c>
+      <c r="K120" s="9">
+        <v>1.06</v>
+      </c>
+      <c r="L120" s="8">
+        <v>71.3</v>
+      </c>
+      <c r="M120" s="9">
+        <v>1.06</v>
+      </c>
+      <c r="N120" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O120" s="8">
+        <v>71.3</v>
+      </c>
+      <c r="P120" s="9">
+        <v>1.06</v>
+      </c>
+      <c r="Q120" s="8">
+        <v>71.3</v>
+      </c>
+    </row>
+    <row r="121" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A121" s="6">
+        <v>41244</v>
+      </c>
+      <c r="B121" s="7">
+        <v>9.32</v>
+      </c>
+      <c r="C121" s="7">
+        <v>10.7</v>
+      </c>
+      <c r="D121" s="7">
+        <v>10.95</v>
+      </c>
+      <c r="E121" s="7">
+        <v>9.19</v>
+      </c>
+      <c r="F121" s="8">
+        <v>1.44</v>
+      </c>
+      <c r="G121" s="8">
+        <v>15.55</v>
+      </c>
+      <c r="H121" s="9">
+        <v>0.69899999999999995</v>
+      </c>
+      <c r="I121" s="8">
+        <v>9.64</v>
+      </c>
+      <c r="J121" s="8">
+        <v>36.9</v>
+      </c>
+      <c r="K121" s="9">
+        <v>6.53</v>
+      </c>
+      <c r="L121" s="10">
+        <v>-10.8</v>
+      </c>
+      <c r="M121" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N121" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O121" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P121" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q121" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="122" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A122" s="6">
+        <v>41214</v>
+      </c>
+      <c r="B122" s="7">
+        <v>8.9</v>
+      </c>
+      <c r="C122" s="7">
+        <v>9.26</v>
+      </c>
+      <c r="D122" s="7">
+        <v>9.6999999999999993</v>
+      </c>
+      <c r="E122" s="7">
+        <v>8.6999999999999993</v>
+      </c>
+      <c r="F122" s="8">
+        <v>0.38</v>
+      </c>
+      <c r="G122" s="8">
+        <v>4.28</v>
+      </c>
+      <c r="H122" s="9">
+        <v>0.63800000000000001</v>
+      </c>
+      <c r="I122" s="8">
+        <v>0.65</v>
+      </c>
+      <c r="J122" s="8">
+        <v>16.600000000000001</v>
+      </c>
+      <c r="K122" s="9">
+        <v>5.83</v>
+      </c>
+      <c r="L122" s="10">
+        <v>-14.4</v>
+      </c>
+      <c r="M122" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N122" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O122" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P122" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q122" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="123" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A123" s="6">
+        <v>41183</v>
+      </c>
+      <c r="B123" s="7">
+        <v>11.1</v>
+      </c>
+      <c r="C123" s="7">
+        <v>8.8800000000000008</v>
+      </c>
+      <c r="D123" s="7">
+        <v>12.8</v>
+      </c>
+      <c r="E123" s="7">
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="F123" s="10">
+        <v>-2.2200000000000002</v>
+      </c>
+      <c r="G123" s="10">
+        <v>-20</v>
+      </c>
+      <c r="H123" s="9">
+        <v>0.63400000000000001</v>
+      </c>
+      <c r="I123" s="8">
+        <v>6.1</v>
+      </c>
+      <c r="J123" s="8">
+        <v>24.4</v>
+      </c>
+      <c r="K123" s="9">
+        <v>5.19</v>
+      </c>
+      <c r="L123" s="10">
+        <v>-17.100000000000001</v>
+      </c>
+      <c r="M123" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N123" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O123" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P123" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q123" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="124" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A124" s="6">
+        <v>41153</v>
+      </c>
+      <c r="B124" s="7">
+        <v>9.99</v>
+      </c>
+      <c r="C124" s="7">
+        <v>11.1</v>
+      </c>
+      <c r="D124" s="7">
+        <v>12.05</v>
+      </c>
+      <c r="E124" s="7">
+        <v>9.7899999999999991</v>
+      </c>
+      <c r="F124" s="8">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="G124" s="8">
+        <v>11.56</v>
+      </c>
+      <c r="H124" s="9">
+        <v>0.59699999999999998</v>
+      </c>
+      <c r="I124" s="8">
+        <v>8.39</v>
+      </c>
+      <c r="J124" s="10">
+        <v>-17.2</v>
+      </c>
+      <c r="K124" s="9">
+        <v>4.5599999999999996</v>
+      </c>
+      <c r="L124" s="10">
+        <v>-20.8</v>
+      </c>
+      <c r="M124" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N124" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O124" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P124" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q124" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="125" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A125" s="6">
+        <v>41122</v>
+      </c>
+      <c r="B125" s="7">
+        <v>8.92</v>
+      </c>
+      <c r="C125" s="7">
+        <v>9.9499999999999993</v>
+      </c>
+      <c r="D125" s="7">
+        <v>10.85</v>
+      </c>
+      <c r="E125" s="7">
+        <v>8.32</v>
+      </c>
+      <c r="F125" s="8">
+        <v>1.23</v>
+      </c>
+      <c r="G125" s="8">
+        <v>14.11</v>
+      </c>
+      <c r="H125" s="9">
+        <v>0.55100000000000005</v>
+      </c>
+      <c r="I125" s="8">
+        <v>30.1</v>
+      </c>
+      <c r="J125" s="8">
+        <v>6.59</v>
+      </c>
+      <c r="K125" s="9">
+        <v>3.96</v>
+      </c>
+      <c r="L125" s="10">
+        <v>-21.3</v>
+      </c>
+      <c r="M125" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N125" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O125" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P125" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q125" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="126" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A126" s="6">
+        <v>41091</v>
+      </c>
+      <c r="B126" s="7">
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="C126" s="7">
+        <v>8.7200000000000006</v>
+      </c>
+      <c r="D126" s="7">
+        <v>9.6999999999999993</v>
+      </c>
+      <c r="E126" s="7">
+        <v>8.6999999999999993</v>
+      </c>
+      <c r="F126" s="10">
+        <v>-0.34</v>
+      </c>
+      <c r="G126" s="10">
+        <v>-3.75</v>
+      </c>
+      <c r="H126" s="9">
+        <v>0.42399999999999999</v>
+      </c>
+      <c r="I126" s="8">
+        <v>2.12</v>
+      </c>
+      <c r="J126" s="10">
+        <v>-22.7</v>
+      </c>
+      <c r="K126" s="9">
+        <v>3.41</v>
+      </c>
+      <c r="L126" s="10">
+        <v>-24.4</v>
+      </c>
+      <c r="M126" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N126" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O126" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P126" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q126" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="127" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A127" s="6">
+        <v>41061</v>
+      </c>
+      <c r="B127" s="7">
+        <v>9.7200000000000006</v>
+      </c>
+      <c r="C127" s="7">
+        <v>9.06</v>
+      </c>
+      <c r="D127" s="7">
+        <v>9.9700000000000006</v>
+      </c>
+      <c r="E127" s="7">
+        <v>8.92</v>
+      </c>
+      <c r="F127" s="10">
+        <v>-0.64</v>
+      </c>
+      <c r="G127" s="10">
+        <v>-6.6</v>
+      </c>
+      <c r="H127" s="9">
+        <v>0.41499999999999998</v>
+      </c>
+      <c r="I127" s="10">
+        <v>-27.7</v>
+      </c>
+      <c r="J127" s="10">
+        <v>-35.6</v>
+      </c>
+      <c r="K127" s="9">
+        <v>2.99</v>
+      </c>
+      <c r="L127" s="10">
+        <v>-24.7</v>
+      </c>
+      <c r="M127" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N127" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O127" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P127" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q127" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="128" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A128" s="6">
+        <v>41030</v>
+      </c>
+      <c r="B128" s="7">
+        <v>10.3</v>
+      </c>
+      <c r="C128" s="7">
+        <v>9.6999999999999993</v>
+      </c>
+      <c r="D128" s="7">
+        <v>10.7</v>
+      </c>
+      <c r="E128" s="7">
+        <v>9.4</v>
+      </c>
+      <c r="F128" s="10">
+        <v>-0.6</v>
+      </c>
+      <c r="G128" s="10">
+        <v>-5.83</v>
+      </c>
+      <c r="H128" s="9">
+        <v>0.57399999999999995</v>
+      </c>
+      <c r="I128" s="8">
+        <v>12.4</v>
+      </c>
+      <c r="J128" s="10">
+        <v>-20.9</v>
+      </c>
+      <c r="K128" s="9">
+        <v>2.57</v>
+      </c>
+      <c r="L128" s="10">
+        <v>-22.6</v>
+      </c>
+      <c r="M128" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N128" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O128" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P128" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q128" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="129" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A129" s="6">
+        <v>41000</v>
+      </c>
+      <c r="B129" s="7">
+        <v>11.45</v>
+      </c>
+      <c r="C129" s="7">
+        <v>10.3</v>
+      </c>
+      <c r="D129" s="7">
+        <v>11.65</v>
+      </c>
+      <c r="E129" s="7">
+        <v>10.050000000000001</v>
+      </c>
+      <c r="F129" s="10">
+        <v>-1.3</v>
+      </c>
+      <c r="G129" s="10">
+        <v>-11.21</v>
+      </c>
+      <c r="H129" s="9">
+        <v>0.51</v>
+      </c>
+      <c r="I129" s="10">
+        <v>-10.3</v>
+      </c>
+      <c r="J129" s="10">
+        <v>-31.3</v>
+      </c>
+      <c r="K129" s="9">
+        <v>2</v>
+      </c>
+      <c r="L129" s="10">
+        <v>-23</v>
+      </c>
+      <c r="M129" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N129" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O129" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P129" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q129" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="130" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A130" s="6">
+        <v>40969</v>
+      </c>
+      <c r="B130" s="7">
+        <v>13.7</v>
+      </c>
+      <c r="C130" s="7">
+        <v>11.6</v>
+      </c>
+      <c r="D130" s="7">
+        <v>14.4</v>
+      </c>
+      <c r="E130" s="7">
+        <v>11</v>
+      </c>
+      <c r="F130" s="10">
+        <v>-2.4</v>
+      </c>
+      <c r="G130" s="10">
+        <v>-17.14</v>
+      </c>
+      <c r="H130" s="9">
+        <v>0.56899999999999995</v>
+      </c>
+      <c r="I130" s="8">
+        <v>21.6</v>
+      </c>
+      <c r="J130" s="10">
+        <v>-23.4</v>
+      </c>
+      <c r="K130" s="9">
+        <v>1.49</v>
+      </c>
+      <c r="L130" s="10">
+        <v>-19.7</v>
+      </c>
+      <c r="M130" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N130" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O130" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P130" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q130" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="131" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A131" s="6">
+        <v>40940</v>
+      </c>
+      <c r="B131" s="7">
+        <v>10.9</v>
+      </c>
+      <c r="C131" s="7">
+        <v>14</v>
+      </c>
+      <c r="D131" s="7">
+        <v>15.65</v>
+      </c>
+      <c r="E131" s="7">
+        <v>10.9</v>
+      </c>
+      <c r="F131" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="G131" s="8">
+        <v>28.44</v>
+      </c>
+      <c r="H131" s="9">
+        <v>0.46800000000000003</v>
+      </c>
+      <c r="I131" s="8">
+        <v>3.3</v>
+      </c>
+      <c r="J131" s="8">
+        <v>8.8699999999999992</v>
+      </c>
+      <c r="K131" s="9">
+        <v>0.92</v>
+      </c>
+      <c r="L131" s="10">
+        <v>-17.3</v>
+      </c>
+      <c r="M131" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N131" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O131" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P131" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q131" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="132" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A132" s="6">
+        <v>40909</v>
+      </c>
+      <c r="B132" s="7">
+        <v>10.4</v>
+      </c>
+      <c r="C132" s="7">
+        <v>10.9</v>
+      </c>
+      <c r="D132" s="7">
+        <v>11.3</v>
+      </c>
+      <c r="E132" s="7">
+        <v>10</v>
+      </c>
+      <c r="F132" s="8">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="G132" s="8">
+        <v>5.31</v>
+      </c>
+      <c r="H132" s="9">
+        <v>0.45300000000000001</v>
+      </c>
+      <c r="I132" s="10">
+        <v>-11.4</v>
+      </c>
+      <c r="J132" s="10">
+        <v>-33.799999999999997</v>
+      </c>
+      <c r="K132" s="9">
+        <v>0.45300000000000001</v>
+      </c>
+      <c r="L132" s="10">
+        <v>-33.799999999999997</v>
+      </c>
+      <c r="M132" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N132" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O132" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P132" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q132" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="133" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A133" s="6">
+        <v>40878</v>
+      </c>
+      <c r="B133" s="7">
+        <v>10.6</v>
+      </c>
+      <c r="C133" s="7">
+        <v>10.35</v>
+      </c>
+      <c r="D133" s="7">
+        <v>10.85</v>
+      </c>
+      <c r="E133" s="7">
+        <v>9.26</v>
+      </c>
+      <c r="F133" s="10">
+        <v>-0.15</v>
+      </c>
+      <c r="G133" s="10">
+        <v>-1.43</v>
+      </c>
+      <c r="H133" s="9">
+        <v>0.51100000000000001</v>
+      </c>
+      <c r="I133" s="10">
+        <v>-6.6</v>
+      </c>
+      <c r="J133" s="10">
+        <v>-38.6</v>
+      </c>
+      <c r="K133" s="9">
+        <v>7.32</v>
+      </c>
+      <c r="L133" s="10">
+        <v>-47.9</v>
+      </c>
+      <c r="M133" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N133" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O133" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P133" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q133" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="134" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A134" s="6">
+        <v>40848</v>
+      </c>
+      <c r="B134" s="7">
+        <v>12.55</v>
+      </c>
+      <c r="C134" s="7">
+        <v>10.5</v>
+      </c>
+      <c r="D134" s="7">
+        <v>13</v>
+      </c>
+      <c r="E134" s="7">
+        <v>10.5</v>
+      </c>
+      <c r="F134" s="10">
+        <v>-1.95</v>
+      </c>
+      <c r="G134" s="10">
+        <v>-15.66</v>
+      </c>
+      <c r="H134" s="9">
+        <v>0.54700000000000004</v>
+      </c>
+      <c r="I134" s="8">
+        <v>7.37</v>
+      </c>
+      <c r="J134" s="10">
+        <v>-31.4</v>
+      </c>
+      <c r="K134" s="9">
+        <v>6.81</v>
+      </c>
+      <c r="L134" s="10">
+        <v>-48.5</v>
+      </c>
+      <c r="M134" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N134" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O134" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P134" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q134" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="135" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A135" s="6">
+        <v>40817</v>
+      </c>
+      <c r="B135" s="7">
+        <v>12.8</v>
+      </c>
+      <c r="C135" s="7">
+        <v>12.45</v>
+      </c>
+      <c r="D135" s="7">
+        <v>14.5</v>
+      </c>
+      <c r="E135" s="7">
+        <v>12.35</v>
+      </c>
+      <c r="F135" s="10">
+        <v>-0.8</v>
+      </c>
+      <c r="G135" s="10">
+        <v>-6.04</v>
+      </c>
+      <c r="H135" s="9">
+        <v>0.50900000000000001</v>
+      </c>
+      <c r="I135" s="10">
+        <v>-29.4</v>
+      </c>
+      <c r="J135" s="10">
+        <v>-47.5</v>
+      </c>
+      <c r="K135" s="9">
+        <v>6.26</v>
+      </c>
+      <c r="L135" s="10">
+        <v>-49.6</v>
+      </c>
+      <c r="M135" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N135" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O135" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P135" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q135" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="136" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A136" s="6">
+        <v>40787</v>
+      </c>
+      <c r="B136" s="7">
+        <v>11.6</v>
+      </c>
+      <c r="C136" s="7">
+        <v>13.25</v>
+      </c>
+      <c r="D136" s="7">
+        <v>14.2</v>
+      </c>
+      <c r="E136" s="7">
+        <v>11.05</v>
+      </c>
+      <c r="F136" s="8">
+        <v>1.75</v>
+      </c>
+      <c r="G136" s="8">
+        <v>15.22</v>
+      </c>
+      <c r="H136" s="9">
+        <v>0.72099999999999997</v>
+      </c>
+      <c r="I136" s="8">
+        <v>39.6</v>
+      </c>
+      <c r="J136" s="10">
+        <v>-39.9</v>
+      </c>
+      <c r="K136" s="9">
+        <v>5.75</v>
+      </c>
+      <c r="L136" s="10">
+        <v>-49.8</v>
+      </c>
+      <c r="M136" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N136" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O136" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P136" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q136" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="137" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A137" s="6">
+        <v>40756</v>
+      </c>
+      <c r="B137" s="7">
+        <v>15.45</v>
+      </c>
+      <c r="C137" s="7">
+        <v>11.5</v>
+      </c>
+      <c r="D137" s="7">
+        <v>16</v>
+      </c>
+      <c r="E137" s="7">
+        <v>10.9</v>
+      </c>
+      <c r="F137" s="10">
+        <v>-3.95</v>
+      </c>
+      <c r="G137" s="10">
+        <v>-25.57</v>
+      </c>
+      <c r="H137" s="9">
+        <v>0.51700000000000002</v>
+      </c>
+      <c r="I137" s="10">
+        <v>-5.64</v>
+      </c>
+      <c r="J137" s="10">
+        <v>-47.3</v>
+      </c>
+      <c r="K137" s="9">
+        <v>5.03</v>
+      </c>
+      <c r="L137" s="10">
+        <v>-50.9</v>
+      </c>
+      <c r="M137" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N137" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O137" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P137" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q137" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="138" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A138" s="6">
+        <v>40725</v>
+      </c>
+      <c r="B138" s="7">
+        <v>18.600000000000001</v>
+      </c>
+      <c r="C138" s="7">
+        <v>15.45</v>
+      </c>
+      <c r="D138" s="7">
+        <v>19</v>
+      </c>
+      <c r="E138" s="7">
+        <v>14.8</v>
+      </c>
+      <c r="F138" s="10">
+        <v>-3.05</v>
+      </c>
+      <c r="G138" s="10">
+        <v>-16.489999999999998</v>
+      </c>
+      <c r="H138" s="9">
+        <v>0.54800000000000004</v>
+      </c>
+      <c r="I138" s="10">
+        <v>-15</v>
+      </c>
+      <c r="J138" s="10">
+        <v>-42.9</v>
+      </c>
+      <c r="K138" s="9">
+        <v>4.5199999999999996</v>
+      </c>
+      <c r="L138" s="10">
+        <v>-51.3</v>
+      </c>
+      <c r="M138" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N138" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O138" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P138" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q138" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="139" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A139" s="6">
+        <v>40695</v>
+      </c>
+      <c r="B139" s="7">
+        <v>23.3</v>
+      </c>
+      <c r="C139" s="7">
+        <v>18.5</v>
+      </c>
+      <c r="D139" s="7">
+        <v>24</v>
+      </c>
+      <c r="E139" s="7">
+        <v>17.3</v>
+      </c>
+      <c r="F139" s="10">
+        <v>-4.5</v>
+      </c>
+      <c r="G139" s="10">
+        <v>-19.57</v>
+      </c>
+      <c r="H139" s="9">
+        <v>0.64400000000000002</v>
+      </c>
+      <c r="I139" s="10">
+        <v>-11.2</v>
+      </c>
+      <c r="J139" s="10">
+        <v>-46</v>
+      </c>
+      <c r="K139" s="9">
+        <v>3.97</v>
+      </c>
+      <c r="L139" s="10">
+        <v>-52.2</v>
+      </c>
+      <c r="M139" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N139" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O139" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P139" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q139" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="140" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A140" s="6">
+        <v>40664</v>
+      </c>
+      <c r="B140" s="7">
+        <v>29.1</v>
+      </c>
+      <c r="C140" s="7">
+        <v>23</v>
+      </c>
+      <c r="D140" s="7">
+        <v>29.9</v>
+      </c>
+      <c r="E140" s="7">
+        <v>21.95</v>
+      </c>
+      <c r="F140" s="10">
+        <v>-7.4</v>
+      </c>
+      <c r="G140" s="10">
+        <v>-24.34</v>
+      </c>
+      <c r="H140" s="9">
+        <v>0.72599999999999998</v>
+      </c>
+      <c r="I140" s="10">
+        <v>-2.36</v>
+      </c>
+      <c r="J140" s="10">
+        <v>-48.1</v>
+      </c>
+      <c r="K140" s="9">
+        <v>3.32</v>
+      </c>
+      <c r="L140" s="10">
+        <v>-53.3</v>
+      </c>
+      <c r="M140" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N140" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O140" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P140" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q140" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="141" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A141" s="6">
+        <v>40634</v>
+      </c>
+      <c r="B141" s="7">
+        <v>35.799999999999997</v>
+      </c>
+      <c r="C141" s="7">
+        <v>30.4</v>
+      </c>
+      <c r="D141" s="7">
+        <v>35.799999999999997</v>
+      </c>
+      <c r="E141" s="7">
+        <v>30.1</v>
+      </c>
+      <c r="F141" s="10">
+        <v>-5.4</v>
+      </c>
+      <c r="G141" s="10">
+        <v>-15.08</v>
+      </c>
+      <c r="H141" s="9">
+        <v>0.74299999999999999</v>
+      </c>
+      <c r="I141" s="8">
+        <v>0.05</v>
+      </c>
+      <c r="J141" s="10">
+        <v>-46.7</v>
+      </c>
+      <c r="K141" s="9">
+        <v>2.6</v>
+      </c>
+      <c r="L141" s="10">
+        <v>-54.6</v>
+      </c>
+      <c r="M141" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N141" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O141" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P141" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q141" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="142" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A142" s="6">
+        <v>40603</v>
+      </c>
+      <c r="B142" s="7">
+        <v>39.5</v>
+      </c>
+      <c r="C142" s="7">
+        <v>35.799999999999997</v>
+      </c>
+      <c r="D142" s="7">
+        <v>46.4</v>
+      </c>
+      <c r="E142" s="7">
+        <v>35.6</v>
+      </c>
+      <c r="F142" s="10">
+        <v>-3</v>
+      </c>
+      <c r="G142" s="10">
+        <v>-7.73</v>
+      </c>
+      <c r="H142" s="9">
+        <v>0.74299999999999999</v>
+      </c>
+      <c r="I142" s="8">
+        <v>72.900000000000006</v>
+      </c>
+      <c r="J142" s="10">
+        <v>-53.9</v>
+      </c>
+      <c r="K142" s="9">
+        <v>1.86</v>
+      </c>
+      <c r="L142" s="10">
+        <v>-57.1</v>
+      </c>
+      <c r="M142" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N142" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O142" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P142" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q142" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="143" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A143" s="6">
+        <v>40575</v>
+      </c>
+      <c r="B143" s="7">
+        <v>42.55</v>
+      </c>
+      <c r="C143" s="7">
+        <v>38.799999999999997</v>
+      </c>
+      <c r="D143" s="7">
+        <v>44.8</v>
+      </c>
+      <c r="E143" s="7">
+        <v>37.15</v>
+      </c>
+      <c r="F143" s="10">
+        <v>-3.25</v>
+      </c>
+      <c r="G143" s="10">
+        <v>-7.73</v>
+      </c>
+      <c r="H143" s="9">
+        <v>0.43</v>
+      </c>
+      <c r="I143" s="10">
+        <v>-37.1</v>
+      </c>
+      <c r="J143" s="10">
+        <v>-56.2</v>
+      </c>
+      <c r="K143" s="9">
+        <v>1.1100000000000001</v>
+      </c>
+      <c r="L143" s="10">
+        <v>-59</v>
+      </c>
+      <c r="M143" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N143" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O143" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P143" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q143" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="144" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A144" s="6">
+        <v>40544</v>
+      </c>
+      <c r="B144" s="7">
+        <v>33</v>
+      </c>
+      <c r="C144" s="7">
+        <v>42.05</v>
+      </c>
+      <c r="D144" s="7">
+        <v>49.8</v>
+      </c>
+      <c r="E144" s="7">
+        <v>32.6</v>
+      </c>
+      <c r="F144" s="8">
+        <v>9.1</v>
+      </c>
+      <c r="G144" s="8">
+        <v>27.62</v>
+      </c>
+      <c r="H144" s="9">
+        <v>0.68300000000000005</v>
+      </c>
+      <c r="I144" s="10">
+        <v>-17.899999999999999</v>
+      </c>
+      <c r="J144" s="10">
+        <v>-60.5</v>
+      </c>
+      <c r="K144" s="9">
+        <v>0.68300000000000005</v>
+      </c>
+      <c r="L144" s="10">
+        <v>-60.5</v>
+      </c>
+      <c r="M144" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N144" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O144" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P144" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q144" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="145" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A145" s="6">
+        <v>40513</v>
+      </c>
+      <c r="B145" s="7">
+        <v>31.3</v>
+      </c>
+      <c r="C145" s="7">
+        <v>32.950000000000003</v>
+      </c>
+      <c r="D145" s="7">
+        <v>34.9</v>
+      </c>
+      <c r="E145" s="7">
+        <v>31.3</v>
+      </c>
+      <c r="F145" s="8">
+        <v>7.95</v>
+      </c>
+      <c r="G145" s="8">
+        <v>31.8</v>
+      </c>
+      <c r="H145" s="9">
+        <v>0.83199999999999996</v>
+      </c>
+      <c r="I145" s="8">
+        <v>4.3499999999999996</v>
+      </c>
+      <c r="J145" s="10">
+        <v>-45.7</v>
+      </c>
+      <c r="K145" s="9">
+        <v>14.05</v>
+      </c>
+      <c r="L145" s="10">
+        <v>-31.6</v>
+      </c>
+      <c r="M145" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N145" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O145" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P145" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q145" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="146" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A146" s="6">
+        <v>40483</v>
+      </c>
+      <c r="B146" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C146" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D146" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E146" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F146" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G146" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H146" s="9">
+        <v>0.79700000000000004</v>
+      </c>
+      <c r="I146" s="10">
+        <v>-17.8</v>
+      </c>
+      <c r="J146" s="10">
+        <v>-51.5</v>
+      </c>
+      <c r="K146" s="9">
+        <v>13.22</v>
+      </c>
+      <c r="L146" s="10">
+        <v>-30.5</v>
+      </c>
+      <c r="M146" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N146" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O146" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P146" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q146" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="147" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A147" s="6">
+        <v>40452</v>
+      </c>
+      <c r="B147" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C147" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D147" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E147" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F147" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G147" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H147" s="9">
+        <v>0.97</v>
+      </c>
+      <c r="I147" s="10">
+        <v>-19.2</v>
+      </c>
+      <c r="J147" s="10">
+        <v>-43.8</v>
+      </c>
+      <c r="K147" s="9">
+        <v>12.42</v>
+      </c>
+      <c r="L147" s="10">
+        <v>-28.5</v>
+      </c>
+      <c r="M147" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N147" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O147" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P147" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q147" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="148" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A148" s="6">
+        <v>40422</v>
+      </c>
+      <c r="B148" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C148" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D148" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E148" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F148" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G148" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H148" s="9">
+        <v>1.2</v>
+      </c>
+      <c r="I148" s="8">
+        <v>22.4</v>
+      </c>
+      <c r="J148" s="10">
+        <v>-48.2</v>
+      </c>
+      <c r="K148" s="9">
+        <v>11.45</v>
+      </c>
+      <c r="L148" s="10">
+        <v>-26.8</v>
+      </c>
+      <c r="M148" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N148" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O148" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P148" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q148" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="149" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A149" s="6">
+        <v>40391</v>
+      </c>
+      <c r="B149" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C149" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D149" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E149" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F149" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G149" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H149" s="9">
+        <v>0.98099999999999998</v>
+      </c>
+      <c r="I149" s="8">
+        <v>2.15</v>
+      </c>
+      <c r="J149" s="10">
+        <v>-49.8</v>
+      </c>
+      <c r="K149" s="9">
+        <v>10.25</v>
+      </c>
+      <c r="L149" s="10">
+        <v>-23.2</v>
+      </c>
+      <c r="M149" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N149" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O149" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P149" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q149" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="150" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A150" s="6">
+        <v>40360</v>
+      </c>
+      <c r="B150" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C150" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D150" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E150" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F150" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G150" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H150" s="9">
+        <v>0.96</v>
+      </c>
+      <c r="I150" s="10">
+        <v>-19.600000000000001</v>
+      </c>
+      <c r="J150" s="10">
+        <v>-50.8</v>
+      </c>
+      <c r="K150" s="9">
+        <v>9.27</v>
+      </c>
+      <c r="L150" s="10">
+        <v>-18.600000000000001</v>
+      </c>
+      <c r="M150" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N150" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O150" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P150" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q150" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="151" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A151" s="6">
+        <v>40330</v>
+      </c>
+      <c r="B151" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C151" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D151" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E151" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F151" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G151" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H151" s="9">
+        <v>1.19</v>
+      </c>
+      <c r="I151" s="10">
+        <v>-14.6</v>
+      </c>
+      <c r="J151" s="10">
+        <v>-29.5</v>
+      </c>
+      <c r="K151" s="9">
+        <v>8.31</v>
+      </c>
+      <c r="L151" s="10">
+        <v>-11.9</v>
+      </c>
+      <c r="M151" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N151" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O151" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P151" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q151" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="152" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A152" s="6">
+        <v>40299</v>
+      </c>
+      <c r="B152" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C152" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D152" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E152" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F152" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G152" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H152" s="9">
+        <v>1.4</v>
+      </c>
+      <c r="I152" s="8">
+        <v>0.17</v>
+      </c>
+      <c r="J152" s="8">
+        <v>6.78</v>
+      </c>
+      <c r="K152" s="9">
+        <v>7.12</v>
+      </c>
+      <c r="L152" s="10">
+        <v>-8.06</v>
+      </c>
+      <c r="M152" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N152" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O152" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P152" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q152" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="153" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A153" s="6">
+        <v>40269</v>
+      </c>
+      <c r="B153" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C153" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D153" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E153" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F153" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G153" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H153" s="9">
+        <v>1.4</v>
+      </c>
+      <c r="I153" s="10">
+        <v>-13.4</v>
+      </c>
+      <c r="J153" s="10">
+        <v>-24.6</v>
+      </c>
+      <c r="K153" s="9">
+        <v>5.72</v>
+      </c>
+      <c r="L153" s="10">
+        <v>-11.1</v>
+      </c>
+      <c r="M153" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N153" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O153" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P153" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q153" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="154" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A154" s="6">
+        <v>40238</v>
+      </c>
+      <c r="B154" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C154" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D154" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E154" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F154" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G154" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H154" s="9">
+        <v>1.61</v>
+      </c>
+      <c r="I154" s="8">
+        <v>64.400000000000006</v>
+      </c>
+      <c r="J154" s="10">
+        <v>-19.399999999999999</v>
+      </c>
+      <c r="K154" s="9">
+        <v>4.32</v>
+      </c>
+      <c r="L154" s="10">
+        <v>-5.63</v>
+      </c>
+      <c r="M154" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N154" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O154" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P154" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q154" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="155" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A155" s="6">
+        <v>40210</v>
+      </c>
+      <c r="B155" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C155" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D155" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E155" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F155" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G155" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H155" s="9">
+        <v>0.98099999999999998</v>
+      </c>
+      <c r="I155" s="10">
+        <v>-43.4</v>
+      </c>
+      <c r="J155" s="10">
+        <v>-28.9</v>
+      </c>
+      <c r="K155" s="9">
+        <v>2.71</v>
+      </c>
+      <c r="L155" s="8">
+        <v>5.04</v>
+      </c>
+      <c r="M155" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N155" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O155" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P155" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q155" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="156" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A156" s="6">
+        <v>40179</v>
+      </c>
+      <c r="B156" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C156" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D156" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E156" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F156" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G156" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H156" s="9">
+        <v>1.73</v>
+      </c>
+      <c r="I156" s="8">
+        <v>12.9</v>
+      </c>
+      <c r="J156" s="8">
+        <v>44</v>
+      </c>
+      <c r="K156" s="9">
+        <v>1.73</v>
+      </c>
+      <c r="L156" s="8">
+        <v>44</v>
+      </c>
+      <c r="M156" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N156" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O156" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P156" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q156" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="157" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A157" s="6">
+        <v>40148</v>
+      </c>
+      <c r="B157" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C157" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D157" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E157" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F157" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G157" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H157" s="9">
+        <v>1.53</v>
+      </c>
+      <c r="I157" s="10">
+        <v>-6.77</v>
+      </c>
+      <c r="J157" s="8">
+        <v>73.599999999999994</v>
+      </c>
+      <c r="K157" s="9">
+        <v>20.56</v>
+      </c>
+      <c r="L157" s="10">
+        <v>-1.71</v>
+      </c>
+      <c r="M157" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N157" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O157" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P157" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q157" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="158" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A158" s="6">
+        <v>40118</v>
+      </c>
+      <c r="B158" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C158" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D158" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E158" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F158" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G158" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H158" s="9">
+        <v>1.64</v>
+      </c>
+      <c r="I158" s="10">
+        <v>-4.59</v>
+      </c>
+      <c r="J158" s="8">
+        <v>14.4</v>
+      </c>
+      <c r="K158" s="9">
+        <v>19.02</v>
+      </c>
+      <c r="L158" s="10">
+        <v>-5.03</v>
+      </c>
+      <c r="M158" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N158" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O158" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P158" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q158" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="159" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A159" s="6">
+        <v>39753</v>
+      </c>
+      <c r="B159" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C159" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D159" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E159" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F159" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G159" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H159" s="9">
+        <v>1.44</v>
+      </c>
+      <c r="I159" s="10">
+        <v>-39.200000000000003</v>
+      </c>
+      <c r="J159" s="10">
+        <v>-10.7</v>
+      </c>
+      <c r="K159" s="9">
+        <v>20.03</v>
+      </c>
+      <c r="L159" s="8">
+        <v>15.9</v>
+      </c>
+      <c r="M159" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N159" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O159" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P159" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q159" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="160" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A160" s="6">
+        <v>39722</v>
+      </c>
+      <c r="B160" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C160" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D160" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E160" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F160" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G160" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H160" s="9">
+        <v>2.37</v>
+      </c>
+      <c r="I160" s="10">
+        <v>-4.01</v>
+      </c>
+      <c r="J160" s="8">
+        <v>25.4</v>
+      </c>
+      <c r="K160" s="9">
+        <v>18.600000000000001</v>
+      </c>
+      <c r="L160" s="8">
+        <v>18.600000000000001</v>
+      </c>
+      <c r="M160" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N160" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O160" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P160" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q160" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="161" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A161" s="6">
+        <v>39692</v>
+      </c>
+      <c r="B161" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C161" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D161" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E161" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F161" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G161" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H161" s="9">
+        <v>2.46</v>
+      </c>
+      <c r="I161" s="8">
+        <v>19.3</v>
+      </c>
+      <c r="J161" s="8">
+        <v>20.7</v>
+      </c>
+      <c r="K161" s="9">
+        <v>16.23</v>
+      </c>
+      <c r="L161" s="8">
+        <v>17.7</v>
+      </c>
+      <c r="M161" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N161" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O161" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P161" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q161" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="162" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A162" s="6">
+        <v>39661</v>
+      </c>
+      <c r="B162" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C162" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D162" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E162" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F162" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G162" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H162" s="9">
+        <v>2.0699999999999998</v>
+      </c>
+      <c r="I162" s="10">
+        <v>-3.21</v>
+      </c>
+      <c r="J162" s="8">
+        <v>6.84</v>
+      </c>
+      <c r="K162" s="9">
+        <v>13.77</v>
+      </c>
+      <c r="L162" s="8">
+        <v>17.2</v>
+      </c>
+      <c r="M162" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N162" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O162" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P162" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q162" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="163" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A163" s="6">
+        <v>39630</v>
+      </c>
+      <c r="B163" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C163" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D163" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E163" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F163" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G163" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H163" s="9">
+        <v>2.13</v>
+      </c>
+      <c r="I163" s="8">
+        <v>44.1</v>
+      </c>
+      <c r="J163" s="8">
+        <v>28.7</v>
+      </c>
+      <c r="K163" s="9">
+        <v>11.7</v>
+      </c>
+      <c r="L163" s="8">
+        <v>19.2</v>
+      </c>
+      <c r="M163" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N163" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O163" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P163" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q163" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="164" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A164" s="6">
+        <v>39600</v>
+      </c>
+      <c r="B164" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C164" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D164" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E164" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F164" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G164" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H164" s="9">
+        <v>1.48</v>
+      </c>
+      <c r="I164" s="10">
+        <v>-2.38</v>
+      </c>
+      <c r="J164" s="8">
+        <v>14.9</v>
+      </c>
+      <c r="K164" s="9">
+        <v>9.57</v>
+      </c>
+      <c r="L164" s="8">
+        <v>17.3</v>
+      </c>
+      <c r="M164" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N164" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O164" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P164" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q164" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="165" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A165" s="6">
+        <v>39569</v>
+      </c>
+      <c r="B165" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C165" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D165" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E165" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F165" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G165" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H165" s="9">
+        <v>1.52</v>
+      </c>
+      <c r="I165" s="10">
+        <v>-14.6</v>
+      </c>
+      <c r="J165" s="8">
+        <v>21.9</v>
+      </c>
+      <c r="K165" s="9">
+        <v>8.09</v>
+      </c>
+      <c r="L165" s="8">
+        <v>17.8</v>
+      </c>
+      <c r="M165" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N165" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O165" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P165" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q165" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="166" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A166" s="6">
+        <v>39539</v>
+      </c>
+      <c r="B166" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C166" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D166" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E166" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F166" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G166" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H166" s="9">
+        <v>1.78</v>
+      </c>
+      <c r="I166" s="8">
+        <v>1.45</v>
+      </c>
+      <c r="J166" s="8">
+        <v>16.899999999999999</v>
+      </c>
+      <c r="K166" s="9">
+        <v>6.57</v>
+      </c>
+      <c r="L166" s="8">
+        <v>16.899999999999999</v>
+      </c>
+      <c r="M166" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N166" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O166" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P166" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q166" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="167" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A167" s="6">
+        <v>39508</v>
+      </c>
+      <c r="B167" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C167" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D167" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E167" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F167" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G167" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H167" s="9">
+        <v>1.75</v>
+      </c>
+      <c r="I167" s="8">
+        <v>38</v>
+      </c>
+      <c r="J167" s="8">
+        <v>13.8</v>
+      </c>
+      <c r="K167" s="9">
+        <v>4.79</v>
+      </c>
+      <c r="L167" s="8">
+        <v>16.8</v>
+      </c>
+      <c r="M167" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N167" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O167" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P167" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q167" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="168" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A168" s="6">
+        <v>39479</v>
+      </c>
+      <c r="B168" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C168" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D168" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E168" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F168" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G168" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H168" s="9">
+        <v>1.27</v>
+      </c>
+      <c r="I168" s="10">
+        <v>-28.6</v>
+      </c>
+      <c r="J168" s="8">
+        <v>16.3</v>
+      </c>
+      <c r="K168" s="9">
+        <v>3.04</v>
+      </c>
+      <c r="L168" s="8">
+        <v>18.600000000000001</v>
+      </c>
+      <c r="M168" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N168" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O168" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P168" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q168" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="169" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A169" s="6">
+        <v>39448</v>
+      </c>
+      <c r="B169" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C169" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D169" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E169" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F169" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G169" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H169" s="9">
+        <v>1.78</v>
+      </c>
+      <c r="I169" s="8">
+        <v>25.8</v>
+      </c>
+      <c r="J169" s="8">
+        <v>20.399999999999999</v>
+      </c>
+      <c r="K169" s="9">
+        <v>1.78</v>
+      </c>
+      <c r="L169" s="8">
+        <v>20.399999999999999</v>
+      </c>
+      <c r="M169" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N169" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O169" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P169" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q169" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="170" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A170" s="6">
+        <v>39417</v>
+      </c>
+      <c r="B170" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C170" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D170" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E170" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F170" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G170" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H170" s="9">
+        <v>1.41</v>
+      </c>
+      <c r="I170" s="10">
+        <v>-12.3</v>
+      </c>
+      <c r="J170" s="8">
+        <v>4.54</v>
+      </c>
+      <c r="K170" s="9">
+        <v>18.690000000000001</v>
+      </c>
+      <c r="L170" s="8">
+        <v>23.7</v>
+      </c>
+      <c r="M170" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N170" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O170" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P170" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q170" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="171" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A171" s="6">
+        <v>39387</v>
+      </c>
+      <c r="B171" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C171" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D171" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E171" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F171" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G171" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H171" s="9">
+        <v>1.61</v>
+      </c>
+      <c r="I171" s="10">
+        <v>-14.7</v>
+      </c>
+      <c r="J171" s="8">
+        <v>0.96</v>
+      </c>
+      <c r="K171" s="9">
+        <v>17.28</v>
+      </c>
+      <c r="L171" s="8">
+        <v>25.6</v>
+      </c>
+      <c r="M171" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N171" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O171" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P171" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q171" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="172" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A172" s="6">
+        <v>39356</v>
+      </c>
+      <c r="B172" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C172" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D172" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E172" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F172" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G172" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H172" s="9">
+        <v>1.89</v>
+      </c>
+      <c r="I172" s="10">
+        <v>-7.63</v>
+      </c>
+      <c r="J172" s="8">
+        <v>20.399999999999999</v>
+      </c>
+      <c r="K172" s="9">
+        <v>15.67</v>
+      </c>
+      <c r="L172" s="8">
+        <v>28.8</v>
+      </c>
+      <c r="M172" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N172" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O172" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P172" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q172" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="173" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A173" s="6">
+        <v>39326</v>
+      </c>
+      <c r="B173" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C173" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D173" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E173" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F173" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G173" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H173" s="9">
+        <v>2.04</v>
+      </c>
+      <c r="I173" s="8">
+        <v>5.6</v>
+      </c>
+      <c r="J173" s="8">
+        <v>26.1</v>
+      </c>
+      <c r="K173" s="9">
+        <v>13.79</v>
+      </c>
+      <c r="L173" s="8">
+        <v>30.1</v>
+      </c>
+      <c r="M173" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N173" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O173" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P173" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q173" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="174" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A174" s="6">
+        <v>39295</v>
+      </c>
+      <c r="B174" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C174" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D174" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E174" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F174" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G174" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H174" s="9">
+        <v>1.93</v>
+      </c>
+      <c r="I174" s="8">
+        <v>16.5</v>
+      </c>
+      <c r="J174" s="8">
+        <v>33.299999999999997</v>
+      </c>
+      <c r="K174" s="9">
+        <v>11.75</v>
+      </c>
+      <c r="L174" s="8">
+        <v>30.8</v>
+      </c>
+      <c r="M174" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N174" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O174" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P174" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q174" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="175" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A175" s="6">
+        <v>39264</v>
+      </c>
+      <c r="B175" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C175" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D175" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E175" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F175" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G175" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H175" s="9">
+        <v>1.66</v>
+      </c>
+      <c r="I175" s="8">
+        <v>28.7</v>
+      </c>
+      <c r="J175" s="8">
+        <v>46.5</v>
+      </c>
+      <c r="K175" s="9">
+        <v>9.81</v>
+      </c>
+      <c r="L175" s="8">
+        <v>30.3</v>
+      </c>
+      <c r="M175" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N175" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O175" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P175" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q175" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="176" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A176" s="6">
+        <v>39234</v>
+      </c>
+      <c r="B176" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C176" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D176" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E176" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F176" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G176" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H176" s="9">
+        <v>1.29</v>
+      </c>
+      <c r="I176" s="8">
+        <v>3.56</v>
+      </c>
+      <c r="J176" s="8">
+        <v>17.3</v>
+      </c>
+      <c r="K176" s="9">
+        <v>8.15</v>
+      </c>
+      <c r="L176" s="8">
+        <v>27.5</v>
+      </c>
+      <c r="M176" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N176" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O176" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P176" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q176" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="177" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A177" s="6">
+        <v>39203</v>
+      </c>
+      <c r="B177" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C177" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D177" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E177" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F177" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G177" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H177" s="9">
+        <v>1.24</v>
+      </c>
+      <c r="I177" s="10">
+        <v>-18</v>
+      </c>
+      <c r="J177" s="8">
+        <v>19.899999999999999</v>
+      </c>
+      <c r="K177" s="9">
+        <v>6.87</v>
+      </c>
+      <c r="L177" s="8">
+        <v>29.6</v>
+      </c>
+      <c r="M177" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N177" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O177" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P177" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q177" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="178" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A178" s="6">
+        <v>39173</v>
+      </c>
+      <c r="B178" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C178" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D178" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E178" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F178" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G178" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H178" s="9">
+        <v>1.52</v>
+      </c>
+      <c r="I178" s="10">
+        <v>-1.22</v>
+      </c>
+      <c r="J178" s="8">
+        <v>33.700000000000003</v>
+      </c>
+      <c r="K178" s="9">
+        <v>5.62</v>
+      </c>
+      <c r="L178" s="8">
+        <v>32</v>
+      </c>
+      <c r="M178" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N178" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O178" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P178" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q178" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="179" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A179" s="6">
+        <v>39142</v>
+      </c>
+      <c r="B179" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C179" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D179" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E179" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F179" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G179" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H179" s="9">
+        <v>1.54</v>
+      </c>
+      <c r="I179" s="8">
+        <v>41</v>
+      </c>
+      <c r="J179" s="8">
+        <v>21.9</v>
+      </c>
+      <c r="K179" s="9">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="L179" s="8">
+        <v>31.3</v>
+      </c>
+      <c r="M179" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N179" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O179" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P179" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q179" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="180" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A180" s="6">
+        <v>39114</v>
+      </c>
+      <c r="B180" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C180" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D180" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E180" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F180" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G180" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H180" s="9">
+        <v>1.0900000000000001</v>
+      </c>
+      <c r="I180" s="10">
+        <v>-26.1</v>
+      </c>
+      <c r="J180" s="8">
+        <v>21</v>
+      </c>
+      <c r="K180" s="9">
+        <v>2.57</v>
+      </c>
+      <c r="L180" s="8">
+        <v>37.700000000000003</v>
+      </c>
+      <c r="M180" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N180" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O180" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P180" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q180" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="181" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A181" s="6">
+        <v>39083</v>
+      </c>
+      <c r="B181" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C181" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D181" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E181" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F181" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G181" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H181" s="9">
+        <v>1.47</v>
+      </c>
+      <c r="I181" s="8">
+        <v>9.31</v>
+      </c>
+      <c r="J181" s="8">
+        <v>53.3</v>
+      </c>
+      <c r="K181" s="9">
+        <v>1.47</v>
+      </c>
+      <c r="L181" s="8">
+        <v>53.3</v>
+      </c>
+      <c r="M181" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N181" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O181" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P181" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q181" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="182" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A182" s="6">
+        <v>39052</v>
+      </c>
+      <c r="B182" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C182" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D182" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E182" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F182" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G182" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H182" s="9">
+        <v>1.35</v>
+      </c>
+      <c r="I182" s="10">
+        <v>-15.3</v>
+      </c>
+      <c r="J182" s="8">
+        <v>31</v>
+      </c>
+      <c r="K182" s="9">
+        <v>15.11</v>
+      </c>
+      <c r="L182" s="8">
+        <v>31.7</v>
+      </c>
+      <c r="M182" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N182" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O182" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P182" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q182" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="183" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A183" s="6">
+        <v>39022</v>
+      </c>
+      <c r="B183" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C183" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D183" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E183" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F183" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G183" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H183" s="9">
+        <v>1.59</v>
+      </c>
+      <c r="I183" s="8">
+        <v>1.78</v>
+      </c>
+      <c r="J183" s="8">
+        <v>61.9</v>
+      </c>
+      <c r="K183" s="9">
+        <v>13.76</v>
+      </c>
+      <c r="L183" s="8">
+        <v>31.8</v>
+      </c>
+      <c r="M183" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N183" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O183" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P183" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q183" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="184" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A184" s="6">
+        <v>38991</v>
+      </c>
+      <c r="B184" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C184" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D184" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E184" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F184" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G184" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H184" s="9">
+        <v>1.57</v>
+      </c>
+      <c r="I184" s="10">
+        <v>-3.26</v>
+      </c>
+      <c r="J184" s="8">
+        <v>37</v>
+      </c>
+      <c r="K184" s="9">
+        <v>12.16</v>
+      </c>
+      <c r="L184" s="8">
+        <v>28.6</v>
+      </c>
+      <c r="M184" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N184" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O184" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P184" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q184" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="185" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A185" s="6">
+        <v>38961</v>
+      </c>
+      <c r="B185" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C185" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D185" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E185" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F185" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G185" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H185" s="9">
+        <v>1.62</v>
+      </c>
+      <c r="I185" s="8">
+        <v>11.6</v>
+      </c>
+      <c r="J185" s="8">
+        <v>31.7</v>
+      </c>
+      <c r="K185" s="9">
+        <v>10.6</v>
+      </c>
+      <c r="L185" s="8">
+        <v>27.5</v>
+      </c>
+      <c r="M185" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N185" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O185" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P185" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q185" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="186" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A186" s="6">
+        <v>38930</v>
+      </c>
+      <c r="B186" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C186" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D186" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E186" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F186" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G186" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H186" s="9">
+        <v>1.45</v>
+      </c>
+      <c r="I186" s="8">
+        <v>28.1</v>
+      </c>
+      <c r="J186" s="8">
+        <v>30.7</v>
+      </c>
+      <c r="K186" s="9">
+        <v>8.98</v>
+      </c>
+      <c r="L186" s="8">
+        <v>26.7</v>
+      </c>
+      <c r="M186" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N186" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O186" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P186" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q186" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="187" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A187" s="6">
+        <v>38899</v>
+      </c>
+      <c r="B187" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C187" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D187" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E187" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F187" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G187" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H187" s="9">
+        <v>1.1299999999999999</v>
+      </c>
+      <c r="I187" s="8">
+        <v>3.01</v>
+      </c>
+      <c r="J187" s="8">
+        <v>15.8</v>
+      </c>
+      <c r="K187" s="9">
+        <v>7.53</v>
+      </c>
+      <c r="L187" s="8">
+        <v>26</v>
+      </c>
+      <c r="M187" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N187" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O187" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P187" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q187" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="188" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A188" s="6">
+        <v>38869</v>
+      </c>
+      <c r="B188" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C188" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D188" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E188" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F188" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G188" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H188" s="9">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="I188" s="8">
+        <v>5.88</v>
+      </c>
+      <c r="J188" s="8">
+        <v>30.1</v>
+      </c>
+      <c r="K188" s="9">
+        <v>6.4</v>
+      </c>
+      <c r="L188" s="8">
+        <v>28</v>
+      </c>
+      <c r="M188" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N188" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O188" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P188" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q188" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="189" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A189" s="6">
+        <v>38838</v>
+      </c>
+      <c r="B189" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C189" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D189" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E189" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F189" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G189" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H189" s="9">
+        <v>1.04</v>
+      </c>
+      <c r="I189" s="10">
+        <v>-8.61</v>
+      </c>
+      <c r="J189" s="8">
+        <v>19.899999999999999</v>
+      </c>
+      <c r="K189" s="9">
+        <v>5.3</v>
+      </c>
+      <c r="L189" s="8">
+        <v>27.6</v>
+      </c>
+      <c r="M189" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N189" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O189" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P189" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q189" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="190" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A190" s="6">
+        <v>38808</v>
+      </c>
+      <c r="B190" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C190" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D190" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E190" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F190" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G190" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H190" s="9">
+        <v>1.1399999999999999</v>
+      </c>
+      <c r="I190" s="10">
+        <v>-9.9</v>
+      </c>
+      <c r="J190" s="8">
+        <v>23.7</v>
+      </c>
+      <c r="K190" s="9">
+        <v>4.26</v>
+      </c>
+      <c r="L190" s="8">
+        <v>46.9</v>
+      </c>
+      <c r="M190" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N190" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O190" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P190" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q190" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="191" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A191" s="6">
+        <v>38777</v>
+      </c>
+      <c r="B191" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C191" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D191" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E191" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F191" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G191" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H191" s="9">
+        <v>1.26</v>
+      </c>
+      <c r="I191" s="8">
+        <v>39.9</v>
+      </c>
+      <c r="J191" s="8">
+        <v>51.7</v>
+      </c>
+      <c r="K191" s="9">
+        <v>3.12</v>
+      </c>
+      <c r="L191" s="8">
+        <v>52.3</v>
+      </c>
+      <c r="M191" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N191" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O191" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P191" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q191" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="192" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A192" s="6">
+        <v>38749</v>
+      </c>
+      <c r="B192" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C192" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D192" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E192" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F192" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G192" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H192" s="9">
+        <v>0.90100000000000002</v>
+      </c>
+      <c r="I192" s="10">
+        <v>-6.37</v>
+      </c>
+      <c r="J192" s="8">
+        <v>152.9</v>
+      </c>
+      <c r="K192" s="9">
+        <v>1.86</v>
+      </c>
+      <c r="L192" s="8">
+        <v>52.8</v>
+      </c>
+      <c r="M192" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N192" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O192" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P192" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q192" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="193" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A193" s="6">
+        <v>38718</v>
+      </c>
+      <c r="B193" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C193" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D193" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E193" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F193" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G193" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H193" s="9">
+        <v>0.96199999999999997</v>
+      </c>
+      <c r="I193" s="10">
+        <v>-6.59</v>
+      </c>
+      <c r="J193" s="8">
+        <v>11.4</v>
+      </c>
+      <c r="K193" s="9">
+        <v>0.96199999999999997</v>
+      </c>
+      <c r="L193" s="8">
+        <v>11.4</v>
+      </c>
+      <c r="M193" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N193" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O193" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P193" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q193" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="194" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A194" s="6">
+        <v>38687</v>
+      </c>
+      <c r="B194" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C194" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D194" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E194" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F194" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G194" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H194" s="9">
+        <v>1.03</v>
+      </c>
+      <c r="I194" s="8">
+        <v>4.6399999999999997</v>
+      </c>
+      <c r="J194" s="8">
+        <v>37.299999999999997</v>
+      </c>
+      <c r="K194" s="9">
+        <v>11.47</v>
+      </c>
+      <c r="L194" s="8">
+        <v>73.099999999999994</v>
+      </c>
+      <c r="M194" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N194" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O194" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P194" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q194" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="195" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A195" s="6">
+        <v>38657</v>
+      </c>
+      <c r="B195" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C195" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D195" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E195" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F195" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G195" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H195" s="9">
+        <v>0.98399999999999999</v>
+      </c>
+      <c r="I195" s="10">
+        <v>-13.9</v>
+      </c>
+      <c r="J195" s="8">
+        <v>26.2</v>
+      </c>
+      <c r="K195" s="9">
+        <v>10.44</v>
+      </c>
+      <c r="L195" s="8">
+        <v>77.7</v>
+      </c>
+      <c r="M195" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N195" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O195" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P195" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q195" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="196" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A196" s="6">
+        <v>38626</v>
+      </c>
+      <c r="B196" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C196" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D196" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E196" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F196" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G196" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H196" s="9">
+        <v>1.1399999999999999</v>
+      </c>
+      <c r="I196" s="10">
+        <v>-6.99</v>
+      </c>
+      <c r="J196" s="8">
+        <v>50.3</v>
+      </c>
+      <c r="K196" s="9">
+        <v>9.4600000000000009</v>
+      </c>
+      <c r="L196" s="8">
+        <v>60.9</v>
+      </c>
+      <c r="M196" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N196" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O196" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P196" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q196" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="197" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A197" s="6">
+        <v>38596</v>
+      </c>
+      <c r="B197" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C197" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D197" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E197" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F197" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G197" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H197" s="9">
+        <v>1.23</v>
+      </c>
+      <c r="I197" s="8">
+        <v>10.8</v>
+      </c>
+      <c r="J197" s="8">
+        <v>42.5</v>
+      </c>
+      <c r="K197" s="9">
+        <v>8.31</v>
+      </c>
+      <c r="L197" s="8">
+        <v>41.5</v>
+      </c>
+      <c r="M197" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N197" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O197" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P197" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q197" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="198" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A198" s="6">
+        <v>38565</v>
+      </c>
+      <c r="B198" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C198" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D198" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E198" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F198" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G198" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H198" s="9">
+        <v>1.1100000000000001</v>
+      </c>
+      <c r="I198" s="8">
+        <v>52.5</v>
+      </c>
+      <c r="J198" s="8">
+        <v>52.7</v>
+      </c>
+      <c r="K198" s="9">
+        <v>7.09</v>
+      </c>
+      <c r="L198" s="8">
+        <v>20.6</v>
+      </c>
+      <c r="M198" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N198" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O198" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P198" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q198" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="199" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A199" s="6">
+        <v>38534</v>
+      </c>
+      <c r="B199" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C199" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D199" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E199" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F199" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G199" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H199" s="9">
+        <v>0.72699999999999998</v>
+      </c>
+      <c r="I199" s="8">
+        <v>28.9</v>
+      </c>
+      <c r="J199" s="8">
+        <v>17.899999999999999</v>
+      </c>
+      <c r="K199" s="9">
+        <v>5.72</v>
+      </c>
+      <c r="L199" s="8">
+        <v>22.5</v>
+      </c>
+      <c r="M199" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N199" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O199" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P199" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q199" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="200" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A200" s="6">
+        <v>38504</v>
+      </c>
+      <c r="B200" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C200" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D200" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E200" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F200" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G200" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H200" s="9">
+        <v>0.56399999999999995</v>
+      </c>
+      <c r="I200" s="10">
+        <v>-34.200000000000003</v>
+      </c>
+      <c r="J200" s="8">
+        <v>0.23</v>
+      </c>
+      <c r="K200" s="9">
+        <v>4.71</v>
+      </c>
+      <c r="L200" s="8">
+        <v>16.100000000000001</v>
+      </c>
+      <c r="M200" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N200" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O200" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P200" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q200" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="201" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A201" s="6">
+        <v>38473</v>
+      </c>
+      <c r="B201" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C201" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D201" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E201" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F201" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G201" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H201" s="9">
+        <v>0.85799999999999998</v>
+      </c>
+      <c r="I201" s="10">
+        <v>-6.58</v>
+      </c>
+      <c r="J201" s="8">
+        <v>37.4</v>
+      </c>
+      <c r="K201" s="9">
+        <v>4.1399999999999997</v>
+      </c>
+      <c r="L201" s="8">
+        <v>18.7</v>
+      </c>
+      <c r="M201" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N201" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O201" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P201" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q201" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="202" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A202" s="6">
+        <v>38443</v>
+      </c>
+      <c r="B202" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C202" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D202" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E202" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F202" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G202" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H202" s="9">
+        <v>0.91800000000000004</v>
+      </c>
+      <c r="I202" s="8">
+        <v>10.5</v>
+      </c>
+      <c r="J202" s="8">
+        <v>38</v>
+      </c>
+      <c r="K202" s="9">
+        <v>2.9</v>
+      </c>
+      <c r="L202" s="8">
+        <v>1.0900000000000001</v>
+      </c>
+      <c r="M202" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N202" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O202" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P202" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q202" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="203" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A203" s="6">
+        <v>38412</v>
+      </c>
+      <c r="B203" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C203" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D203" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E203" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F203" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G203" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H203" s="9">
+        <v>0.83099999999999996</v>
+      </c>
+      <c r="I203" s="8">
+        <v>133.30000000000001</v>
+      </c>
+      <c r="J203" s="10">
+        <v>-8.7200000000000006</v>
+      </c>
+      <c r="K203" s="9">
+        <v>2.0499999999999998</v>
+      </c>
+      <c r="L203" s="10">
+        <v>-6.88</v>
+      </c>
+      <c r="M203" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N203" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O203" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P203" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q203" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="204" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A204" s="6">
+        <v>38384</v>
+      </c>
+      <c r="B204" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C204" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D204" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E204" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F204" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G204" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H204" s="9">
+        <v>0.35599999999999998</v>
+      </c>
+      <c r="I204" s="10">
+        <v>-58.8</v>
+      </c>
+      <c r="J204" s="10">
+        <v>-52.5</v>
+      </c>
+      <c r="K204" s="9">
+        <v>8.6</v>
+      </c>
+      <c r="L204" s="8">
+        <v>565.70000000000005</v>
+      </c>
+      <c r="M204" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N204" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O204" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P204" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q204" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="205" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A205" s="6">
+        <v>38353</v>
+      </c>
+      <c r="B205" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C205" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D205" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E205" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F205" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G205" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H205" s="9">
+        <v>0.86399999999999999</v>
+      </c>
+      <c r="I205" s="8">
+        <v>15.1</v>
+      </c>
+      <c r="J205" s="8">
+        <v>59.2</v>
+      </c>
+      <c r="K205" s="9">
+        <v>0.86299999999999999</v>
+      </c>
+      <c r="L205" s="8">
+        <v>59.1</v>
+      </c>
+      <c r="M205" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N205" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O205" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P205" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q205" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="206" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A206" s="6">
+        <v>38322</v>
+      </c>
+      <c r="B206" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C206" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D206" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E206" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F206" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G206" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H206" s="9">
+        <v>0.75</v>
+      </c>
+      <c r="I206" s="10">
+        <v>-3.82</v>
+      </c>
+      <c r="J206" s="10">
+        <v>-12.2</v>
+      </c>
+      <c r="K206" s="9">
+        <v>6.63</v>
+      </c>
+      <c r="L206" s="8">
+        <v>12.8</v>
+      </c>
+      <c r="M206" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N206" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O206" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P206" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q206" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="207" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A207" s="6">
+        <v>38292</v>
+      </c>
+      <c r="B207" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C207" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D207" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E207" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F207" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G207" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H207" s="9">
+        <v>0.78</v>
+      </c>
+      <c r="I207" s="8">
+        <v>2.62</v>
+      </c>
+      <c r="J207" s="10">
+        <v>-12.8</v>
+      </c>
+      <c r="K207" s="9">
+        <v>5.88</v>
+      </c>
+      <c r="L207" s="8">
+        <v>1065.5999999999999</v>
+      </c>
+      <c r="M207" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N207" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O207" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P207" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q207" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="208" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A208" s="6">
+        <v>38261</v>
+      </c>
+      <c r="B208" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C208" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D208" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E208" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F208" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G208" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H208" s="9">
+        <v>0.76</v>
+      </c>
+      <c r="I208" s="10">
+        <v>-11.8</v>
+      </c>
+      <c r="J208" s="10">
+        <v>-18.3</v>
+      </c>
+      <c r="K208" s="9">
+        <v>5.88</v>
+      </c>
+      <c r="L208" s="8">
+        <v>40.799999999999997</v>
+      </c>
+      <c r="M208" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N208" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O208" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P208" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q208" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="209" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A209" s="6">
+        <v>38231</v>
+      </c>
+      <c r="B209" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C209" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D209" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E209" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F209" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G209" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H209" s="9">
+        <v>0.86199999999999999</v>
+      </c>
+      <c r="I209" s="8">
+        <v>18.7</v>
+      </c>
+      <c r="J209" s="8">
+        <v>2.4500000000000002</v>
+      </c>
+      <c r="K209" s="9">
+        <v>5.88</v>
+      </c>
+      <c r="L209" s="8">
+        <v>76.099999999999994</v>
+      </c>
+      <c r="M209" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N209" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O209" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P209" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q209" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="210" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A210" s="6">
+        <v>38200</v>
+      </c>
+      <c r="B210" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C210" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D210" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E210" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F210" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G210" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H210" s="9">
+        <v>0.72699999999999998</v>
+      </c>
+      <c r="I210" s="8">
+        <v>17.8</v>
+      </c>
+      <c r="J210" s="8">
+        <v>4.62</v>
+      </c>
+      <c r="K210" s="9">
+        <v>5.88</v>
+      </c>
+      <c r="L210" s="8">
+        <v>135.5</v>
+      </c>
+      <c r="M210" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N210" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O210" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P210" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q210" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="211" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A211" s="6">
+        <v>38169</v>
+      </c>
+      <c r="B211" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C211" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D211" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E211" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F211" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G211" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H211" s="9">
+        <v>0.61699999999999999</v>
+      </c>
+      <c r="I211" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J211" s="8">
+        <v>16.899999999999999</v>
+      </c>
+      <c r="K211" s="9">
+        <v>5.88</v>
+      </c>
+      <c r="L211" s="8">
+        <v>226.2</v>
+      </c>
+      <c r="M211" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N211" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O211" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P211" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q211" s="9" t="s">
+        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -4521,7 +12374,7 @@
     <mergeCell ref="H2:J2"/>
     <mergeCell ref="K2:L2"/>
   </mergeCells>
-  <phoneticPr fontId="24" type="noConversion"/>
+  <phoneticPr fontId="25" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>